--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0106F507-2DC0-43A4-BCD6-D174BEB4EC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF93D86E-5E1A-41F8-A73E-47A300A18FE1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1825,7 +1825,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1884,6 +1884,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2070,7 +2074,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -2089,7 +2093,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -9005,56 +9009,56 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="19"/>
+      <c r="P38" s="28"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="6"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="12"/>
+      <c r="W38" s="29"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
-      <c r="AD38" s="12"/>
+      <c r="AD38" s="29"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
       <c r="AJ38" s="3"/>
-      <c r="AK38" s="12"/>
+      <c r="AK38" s="29"/>
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="1"/>
-      <c r="AR38" s="12"/>
+      <c r="AR38" s="29"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
       <c r="AW38" s="3"/>
       <c r="AX38" s="1"/>
-      <c r="AY38" s="12"/>
+      <c r="AY38" s="29"/>
       <c r="AZ38" s="3"/>
       <c r="BA38" s="3"/>
       <c r="BB38" s="3"/>
       <c r="BC38" s="3"/>
       <c r="BD38" s="3"/>
       <c r="BE38" s="1"/>
-      <c r="BF38" s="12"/>
+      <c r="BF38" s="29"/>
       <c r="BG38" s="3"/>
       <c r="BH38" s="3"/>
       <c r="BI38" s="3"/>
       <c r="BJ38" s="3"/>
       <c r="BK38" s="3"/>
       <c r="BL38" s="1"/>
-      <c r="BM38" s="12"/>
+      <c r="BM38" s="29"/>
       <c r="BN38" s="3"/>
       <c r="BO38" s="3"/>
       <c r="BP38" s="3"/>
@@ -9439,15 +9443,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100949757B2A3935B4A84A5374E630DBD2B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7a6d292a2f6a949c3af71fa212296ad8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="337ea2d0-885f-4217-baff-63e0aa38c74f" xmlns:ns3="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20a9319f435276383e25e3a27c1527eb" ns2:_="" ns3:_="">
     <xsd:import namespace="337ea2d0-885f-4217-baff-63e0aa38c74f"/>
@@ -9674,6 +9669,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9693,11 +9697,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="698" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF93D86E-5E1A-41F8-A73E-47A300A18FE1}"/>
+  <xr:revisionPtr revIDLastSave="732" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{303188DD-F5F7-46DC-B879-6AF5C4C1FA61}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="572">
   <si>
     <t>Id</t>
   </si>
@@ -1082,7 +1082,7 @@
     <t>B-1993-C1-0665</t>
   </si>
   <si>
-    <t>27/09/23</t>
+    <t>27/09/2023</t>
   </si>
   <si>
     <t>B-1993-A1-0264</t>
@@ -1094,15 +1094,9 @@
     <t>G-1184-B1-0540</t>
   </si>
   <si>
-    <t>28/04/24</t>
-  </si>
-  <si>
     <t>B-1993-B1-0902</t>
   </si>
   <si>
-    <t>19/10/23</t>
-  </si>
-  <si>
     <t>https://icateltelematica.sharepoint.com/sites/Atividadessemanais-Planejamento/Shared%20Documents/LABORAT%C3%93RIO/Lista%20Baterias/Apps/Microsoft%20Forms/Controle%20de%20Bancos%20de%20Bateria%20Oficial/Relat%C3%B3rio/Banco%20de%20Baterias%20G4%20-%200020743_Denilson%20de%20Oliveira.pdf</t>
   </si>
   <si>
@@ -1160,9 +1154,6 @@
     <t>B-1993-B1-0896</t>
   </si>
   <si>
-    <t>3,55</t>
-  </si>
-  <si>
     <t>B-1993-B1-0664</t>
   </si>
   <si>
@@ -1301,9 +1292,6 @@
     <t>B-1653-B1-0807</t>
   </si>
   <si>
-    <t>28/06/23</t>
-  </si>
-  <si>
     <t>11.51</t>
   </si>
   <si>
@@ -1442,9 +1430,6 @@
     <t>G-1184-B1-0685</t>
   </si>
   <si>
-    <t>12,94</t>
-  </si>
-  <si>
     <t>G-1184-B1-0614</t>
   </si>
   <si>
@@ -1725,9 +1710,6 @@
   </si>
   <si>
     <t>G-2605-A3-0104</t>
-  </si>
-  <si>
-    <t>29/0920/25</t>
   </si>
   <si>
     <t>G-2605-A3-0103</t>
@@ -1825,7 +1807,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1843,7 +1825,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1884,10 +1865,18 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3016,7 +3005,7 @@
     <col min="7" max="7" width="16.85546875" customWidth="1"/>
     <col min="8" max="9" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" style="13" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" style="4" bestFit="1" customWidth="1"/>
@@ -3049,53 +3038,53 @@
     <col min="71" max="71" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="22" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:71" s="21" customFormat="1" ht="40.5" customHeight="1">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="21" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="21" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="8" t="s">
@@ -3116,7 +3105,7 @@
       <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="W1" s="21" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="8" t="s">
@@ -3125,7 +3114,7 @@
       <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="23" t="s">
+      <c r="Z1" s="22" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="8" t="s">
@@ -3137,7 +3126,7 @@
       <c r="AC1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="22" t="s">
+      <c r="AD1" s="21" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="8" t="s">
@@ -3158,7 +3147,7 @@
       <c r="AJ1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="22" t="s">
+      <c r="AK1" s="21" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="8" t="s">
@@ -3179,7 +3168,7 @@
       <c r="AQ1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="22" t="s">
+      <c r="AR1" s="21" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="8" t="s">
@@ -3200,7 +3189,7 @@
       <c r="AX1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="22" t="s">
+      <c r="AY1" s="21" t="s">
         <v>50</v>
       </c>
       <c r="AZ1" s="8" t="s">
@@ -3221,7 +3210,7 @@
       <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="22" t="s">
+      <c r="BF1" s="21" t="s">
         <v>57</v>
       </c>
       <c r="BG1" s="8" t="s">
@@ -3242,7 +3231,7 @@
       <c r="BL1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="22" t="s">
+      <c r="BM1" s="21" t="s">
         <v>64</v>
       </c>
       <c r="BN1" s="8" t="s">
@@ -3260,7 +3249,7 @@
       <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="22" t="s">
+      <c r="BS1" s="21" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3268,10 +3257,10 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>45901.743993055556</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>45901.745532407411</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -3280,7 +3269,7 @@
       <c r="E2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>45708</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -3292,7 +3281,7 @@
       <c r="I2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
         <v>76</v>
       </c>
       <c r="L2" s="2"/>
@@ -3302,7 +3291,7 @@
       <c r="N2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="17"/>
+      <c r="P2" s="16"/>
       <c r="S2" s="8" t="s">
         <v>79</v>
       </c>
@@ -3351,10 +3340,10 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="23">
         <v>45901.747824074097</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>45901.750150462998</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -3363,7 +3352,7 @@
       <c r="E3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>45714</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -3375,7 +3364,7 @@
       <c r="I3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>76</v>
       </c>
       <c r="L3" s="2"/>
@@ -3385,7 +3374,7 @@
       <c r="N3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P3" s="17"/>
+      <c r="P3" s="16"/>
       <c r="S3" s="8" t="s">
         <v>91</v>
       </c>
@@ -3470,10 +3459,10 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>45902.610358796301</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>45902.612789351901</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -3482,7 +3471,7 @@
       <c r="E4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>45847</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -3494,7 +3483,7 @@
       <c r="I4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="14" t="s">
         <v>76</v>
       </c>
       <c r="L4" s="2"/>
@@ -3504,7 +3493,7 @@
       <c r="N4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P4" s="17"/>
+      <c r="P4" s="16"/>
       <c r="Q4" s="3" t="s">
         <v>110</v>
       </c>
@@ -3592,10 +3581,10 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>45958.420960648102</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>45958.426967592597</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -3604,7 +3593,7 @@
       <c r="E5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>45708</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -3616,7 +3605,7 @@
       <c r="I5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="15"/>
+      <c r="K5" s="14"/>
       <c r="L5" s="2"/>
       <c r="M5" s="1" t="s">
         <v>77</v>
@@ -3624,7 +3613,7 @@
       <c r="N5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P5" s="17"/>
+      <c r="P5" s="16"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="6" t="s">
@@ -3693,10 +3682,10 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>45958.427141203698</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>45958.4317592593</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -3705,7 +3694,7 @@
       <c r="E6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>45706</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -3717,7 +3706,7 @@
       <c r="I6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="14"/>
       <c r="L6" s="2"/>
       <c r="M6" s="1" t="s">
         <v>77</v>
@@ -3725,7 +3714,7 @@
       <c r="N6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P6" s="17"/>
+      <c r="P6" s="16"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="6" t="s">
@@ -3821,10 +3810,10 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>45959.681041666699</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>45959.692442129599</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -3833,7 +3822,7 @@
       <c r="E7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>45796</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -3846,7 +3835,7 @@
         <v>75</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="14" t="s">
         <v>135</v>
       </c>
       <c r="L7" s="2">
@@ -3859,7 +3848,7 @@
         <v>90</v>
       </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="17"/>
+      <c r="P7" s="16"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="6" t="s">
@@ -3969,10 +3958,10 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>45959.692546296297</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>45959.704907407402</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -3981,7 +3970,7 @@
       <c r="E8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>45714</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -3994,7 +3983,7 @@
         <v>75</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="15"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="2"/>
       <c r="M8" s="1" t="s">
         <v>77</v>
@@ -4003,7 +3992,7 @@
         <v>90</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="17"/>
+      <c r="P8" s="16"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="6" t="s">
@@ -4111,10 +4100,10 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>45959.704953703702</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>45959.715381944399</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -4123,7 +4112,7 @@
       <c r="E9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>45875</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -4136,7 +4125,7 @@
         <v>150</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="14" t="s">
         <v>151</v>
       </c>
       <c r="L9" s="2">
@@ -4149,7 +4138,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="1"/>
-      <c r="P9" s="17"/>
+      <c r="P9" s="16"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="6" t="s">
@@ -4223,10 +4212,10 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>45959.715451388904</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>45960.369016203702</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -4235,7 +4224,7 @@
       <c r="E10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>45799</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -4248,7 +4237,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="14" t="s">
         <v>155</v>
       </c>
       <c r="L10" s="2"/>
@@ -4259,7 +4248,7 @@
         <v>90</v>
       </c>
       <c r="O10" s="1"/>
-      <c r="P10" s="17"/>
+      <c r="P10" s="16"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="6" t="s">
@@ -4369,10 +4358,10 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>45960.369201388901</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>45960.372916666704</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -4381,7 +4370,7 @@
       <c r="E11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>45797</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -4394,7 +4383,7 @@
         <v>75</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="14" t="s">
         <v>164</v>
       </c>
       <c r="L11" s="2"/>
@@ -4405,7 +4394,7 @@
         <v>90</v>
       </c>
       <c r="O11" s="1"/>
-      <c r="P11" s="17"/>
+      <c r="P11" s="16"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="6" t="s">
@@ -4515,10 +4504,10 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>45960.3730208333</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>45960.383090277799</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -4527,7 +4516,7 @@
       <c r="E12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>45784</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -4540,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="14" t="s">
         <v>173</v>
       </c>
       <c r="L12" s="2">
@@ -4553,7 +4542,7 @@
         <v>90</v>
       </c>
       <c r="O12" s="1"/>
-      <c r="P12" s="17"/>
+      <c r="P12" s="16"/>
       <c r="Q12" s="3" t="s">
         <v>174</v>
       </c>
@@ -4695,10 +4684,10 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>45960.383333333302</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>45960.406053240702</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -4707,7 +4696,7 @@
       <c r="E13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>45800</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -4720,7 +4709,7 @@
         <v>75</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="14" t="s">
         <v>193</v>
       </c>
       <c r="L13" s="2"/>
@@ -4731,7 +4720,7 @@
         <v>90</v>
       </c>
       <c r="O13" s="1"/>
-      <c r="P13" s="17"/>
+      <c r="P13" s="16"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="6" t="s">
@@ -4841,10 +4830,10 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="23">
         <v>45960.406412037002</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="23">
         <v>45960.412141203698</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -4853,7 +4842,7 @@
       <c r="E14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>45818</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -4866,7 +4855,7 @@
         <v>150</v>
       </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="14" t="s">
         <v>202</v>
       </c>
       <c r="L14" s="2"/>
@@ -4877,7 +4866,7 @@
         <v>90</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="P14" s="17"/>
+      <c r="P14" s="16"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="6" t="s">
@@ -4987,10 +4976,10 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>45960.412210648203</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>45960.424756944398</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -4999,7 +4988,7 @@
       <c r="E15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>45869</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -5012,7 +5001,7 @@
         <v>75</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="14" t="s">
         <v>214</v>
       </c>
       <c r="L15" s="2"/>
@@ -5023,7 +5012,7 @@
         <v>90</v>
       </c>
       <c r="O15" s="1"/>
-      <c r="P15" s="17"/>
+      <c r="P15" s="16"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="6" t="s">
@@ -5133,10 +5122,10 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="23">
         <v>45960.431828703702</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <v>45960.435439814799</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -5145,7 +5134,7 @@
       <c r="E16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>45861</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -5158,7 +5147,7 @@
         <v>75</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="14" t="s">
         <v>221</v>
       </c>
       <c r="L16" s="2"/>
@@ -5169,7 +5158,7 @@
         <v>90</v>
       </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="17"/>
+      <c r="P16" s="16"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="6" t="s">
@@ -5279,10 +5268,10 @@
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>45960.436747685198</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>45960.438368055598</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -5291,7 +5280,7 @@
       <c r="E17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>45876</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -5304,7 +5293,7 @@
         <v>75</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="14" t="s">
         <v>225</v>
       </c>
       <c r="L17" s="2"/>
@@ -5315,7 +5304,7 @@
         <v>78</v>
       </c>
       <c r="O17" s="1"/>
-      <c r="P17" s="17"/>
+      <c r="P17" s="16"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="6" t="s">
@@ -5401,10 +5390,10 @@
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <v>45960.4384027778</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>45960.451979166697</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -5413,7 +5402,7 @@
       <c r="E18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>45860</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -5426,7 +5415,7 @@
         <v>150</v>
       </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="14" t="s">
         <v>231</v>
       </c>
       <c r="L18" s="2"/>
@@ -5437,7 +5426,7 @@
         <v>90</v>
       </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="17"/>
+      <c r="P18" s="16"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="6" t="s">
@@ -5547,10 +5536,10 @@
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="23">
         <v>45960.452372685198</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <v>45960.456840277802</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -5559,7 +5548,7 @@
       <c r="E19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>45937</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -5572,7 +5561,7 @@
         <v>150</v>
       </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="14" t="s">
         <v>238</v>
       </c>
       <c r="L19" s="2">
@@ -5585,7 +5574,7 @@
         <v>90</v>
       </c>
       <c r="O19" s="1"/>
-      <c r="P19" s="17"/>
+      <c r="P19" s="16"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="6" t="s">
@@ -5693,10 +5682,10 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <v>45972.4156828704</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>45972.426412036999</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -5705,7 +5694,7 @@
       <c r="E20" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>45883</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -5718,7 +5707,7 @@
         <v>150</v>
       </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="14" t="s">
         <v>242</v>
       </c>
       <c r="L20" s="2"/>
@@ -5731,7 +5720,7 @@
       <c r="O20" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="P20" s="17"/>
+      <c r="P20" s="16"/>
       <c r="Q20" s="3" t="s">
         <v>244</v>
       </c>
@@ -5879,10 +5868,10 @@
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="23">
         <v>45985.611944444398</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="23">
         <v>45985.627962963001</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -5891,7 +5880,7 @@
       <c r="E21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <v>45985</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -5904,7 +5893,7 @@
         <v>150</v>
       </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="14" t="s">
         <v>262</v>
       </c>
       <c r="L21" s="2">
@@ -5919,7 +5908,7 @@
       <c r="O21" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="P21" s="18">
+      <c r="P21" s="17">
         <v>45410</v>
       </c>
       <c r="Q21" s="3" t="s">
@@ -5938,7 +5927,7 @@
       <c r="V21" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="28">
         <v>45410</v>
       </c>
       <c r="X21" s="3" t="s">
@@ -5957,7 +5946,7 @@
       <c r="AC21" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AD21" s="28">
         <v>45410</v>
       </c>
       <c r="AE21" s="3" t="s">
@@ -5978,7 +5967,7 @@
       <c r="AJ21" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="AK21" s="2">
+      <c r="AK21" s="29">
         <v>45410</v>
       </c>
       <c r="AL21" s="3" t="s">
@@ -5997,7 +5986,7 @@
       <c r="AQ21" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="AR21" s="2">
+      <c r="AR21" s="29">
         <v>45410</v>
       </c>
       <c r="AS21" s="3" t="s">
@@ -6016,7 +6005,7 @@
       <c r="AX21" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="AY21" s="2">
+      <c r="AY21" s="29">
         <v>45410</v>
       </c>
       <c r="AZ21" s="3" t="s">
@@ -6035,7 +6024,7 @@
       <c r="BE21" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="BF21" s="2">
+      <c r="BF21" s="29">
         <v>45410</v>
       </c>
       <c r="BG21" s="3" t="s">
@@ -6054,7 +6043,7 @@
       <c r="BL21" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="BM21" s="2">
+      <c r="BM21" s="29">
         <v>45410</v>
       </c>
       <c r="BN21" s="3" t="s">
@@ -6078,10 +6067,10 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="23">
         <v>45988.440625000003</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <v>45988.447372685201</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -6090,7 +6079,7 @@
       <c r="E22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="17">
         <v>45987</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -6103,7 +6092,7 @@
         <v>75</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="14" t="s">
         <v>289</v>
       </c>
       <c r="L22" s="2"/>
@@ -6116,7 +6105,7 @@
       <c r="O22" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="P22" s="18">
+      <c r="P22" s="17">
         <v>45411</v>
       </c>
       <c r="Q22" s="3"/>
@@ -6133,7 +6122,7 @@
       <c r="V22" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="W22" s="13">
+      <c r="W22" s="28">
         <v>45410</v>
       </c>
       <c r="X22" s="3"/>
@@ -6150,7 +6139,7 @@
       <c r="AC22" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AD22" s="29">
         <v>45189</v>
       </c>
       <c r="AE22" s="3"/>
@@ -6167,7 +6156,7 @@
       <c r="AJ22" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="AK22" s="2">
+      <c r="AK22" s="29">
         <v>45410</v>
       </c>
       <c r="AL22" s="3"/>
@@ -6184,7 +6173,7 @@
       <c r="AQ22" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="AR22" s="2">
+      <c r="AR22" s="29">
         <v>45410</v>
       </c>
       <c r="AS22" s="3"/>
@@ -6201,7 +6190,7 @@
       <c r="AX22" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AY22" s="2">
+      <c r="AY22" s="29">
         <v>45410</v>
       </c>
       <c r="AZ22" s="3"/>
@@ -6218,7 +6207,7 @@
       <c r="BE22" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="BF22" s="2">
+      <c r="BF22" s="29">
         <v>45410</v>
       </c>
       <c r="BG22" s="3"/>
@@ -6235,7 +6224,7 @@
       <c r="BL22" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="BM22" s="2">
+      <c r="BM22" s="29">
         <v>45410</v>
       </c>
       <c r="BN22" s="3"/>
@@ -6257,10 +6246,10 @@
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>45992.704687500001</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <v>45992.711736111101</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -6269,7 +6258,7 @@
       <c r="E23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <v>45847</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -6282,7 +6271,7 @@
         <v>150</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="15"/>
+      <c r="K23" s="14"/>
       <c r="L23" s="2"/>
       <c r="M23" s="1" t="s">
         <v>77</v>
@@ -6293,7 +6282,7 @@
       <c r="O23" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="P23" s="19" t="s">
+      <c r="P23" s="18" t="s">
         <v>302</v>
       </c>
       <c r="Q23" s="3"/>
@@ -6393,10 +6382,10 @@
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="23">
         <v>46035.400150463</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>46035.447673611103</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -6405,7 +6394,7 @@
       <c r="E24" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="17">
         <v>46035</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -6418,7 +6407,7 @@
         <v>75</v>
       </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="14" t="s">
         <v>311</v>
       </c>
       <c r="L24" s="2">
@@ -6433,7 +6422,7 @@
       <c r="O24" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="P24" s="19" t="s">
+      <c r="P24" s="18" t="s">
         <v>302</v>
       </c>
       <c r="Q24" s="3" t="s">
@@ -6606,10 +6595,10 @@
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="23">
         <v>46042.709467592598</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="23">
         <v>46042.714189814797</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -6618,7 +6607,7 @@
       <c r="E25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="17">
         <v>46042</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -6631,7 +6620,7 @@
         <v>335</v>
       </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="14" t="s">
         <v>336</v>
       </c>
       <c r="L25" s="2">
@@ -6646,7 +6635,7 @@
       <c r="O25" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="P25" s="19" t="s">
+      <c r="P25" s="18" t="s">
         <v>338</v>
       </c>
       <c r="Q25" s="3"/>
@@ -6749,7 +6738,7 @@
         <v>351</v>
       </c>
       <c r="BF25" s="12" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
@@ -6763,10 +6752,10 @@
         <v>126</v>
       </c>
       <c r="BL25" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BM25" s="12" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
@@ -6780,30 +6769,30 @@
         <v>126</v>
       </c>
       <c r="BS25" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:71">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="23">
         <v>46092.483240740701</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="23">
         <v>46092.499652777798</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F26" s="17">
+        <v>46092</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F26" s="18">
-        <v>46092</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>150</v>
@@ -6812,8 +6801,8 @@
         <v>74</v>
       </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="15" t="s">
-        <v>359</v>
+      <c r="K26" s="14" t="s">
+        <v>357</v>
       </c>
       <c r="L26" s="2">
         <v>46100</v>
@@ -6825,16 +6814,16 @@
         <v>90</v>
       </c>
       <c r="O26" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="P26" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>167</v>
@@ -6843,16 +6832,16 @@
         <v>179</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="W26" s="12" t="s">
         <v>346</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>324</v>
@@ -6867,7 +6856,7 @@
         <v>126</v>
       </c>
       <c r="AC26" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AD26" s="12" t="s">
         <v>346</v>
@@ -6882,13 +6871,13 @@
         <v>139</v>
       </c>
       <c r="AH26" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AJ26" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AK26" s="12" t="s">
         <v>346</v>
@@ -6897,19 +6886,19 @@
         <v>316</v>
       </c>
       <c r="AM26" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AN26" s="3" t="s">
         <v>145</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AP26" s="3" t="s">
         <v>82</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AR26" s="12" t="s">
         <v>346</v>
@@ -6918,19 +6907,19 @@
         <v>323</v>
       </c>
       <c r="AT26" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AU26" s="3" t="s">
         <v>139</v>
       </c>
       <c r="AV26" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AW26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AY26" s="12" t="s">
         <v>346</v>
@@ -6939,19 +6928,19 @@
         <v>323</v>
       </c>
       <c r="BA26" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="BB26" s="3" t="s">
         <v>167</v>
       </c>
       <c r="BC26" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="BD26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="BE26" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="BF26" s="12" t="s">
         <v>346</v>
@@ -6960,50 +6949,50 @@
         <v>323</v>
       </c>
       <c r="BH26" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="BI26" s="3" t="s">
         <v>79</v>
       </c>
       <c r="BJ26" s="3" t="s">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="BK26" s="3" t="s">
         <v>82</v>
       </c>
       <c r="BL26" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="BM26" s="12" t="s">
         <v>346</v>
       </c>
       <c r="BN26" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="BO26" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="BP26" s="3" t="s">
         <v>235</v>
       </c>
       <c r="BQ26" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="BR26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="BS26" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:71">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>46105.5940162037</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="23">
         <v>46105.612777777802</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -7012,11 +7001,11 @@
       <c r="E27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="17">
         <v>46099</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>74</v>
@@ -7025,8 +7014,8 @@
         <v>150</v>
       </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="15" t="s">
-        <v>379</v>
+      <c r="K27" s="14" t="s">
+        <v>376</v>
       </c>
       <c r="L27" s="2">
         <v>46122</v>
@@ -7038,16 +7027,16 @@
         <v>90</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="P27" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="P27" s="18" t="s">
         <v>344</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>270</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>160</v>
@@ -7056,10 +7045,10 @@
         <v>106</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="W27" s="12" t="s">
         <v>344</v>
@@ -7068,7 +7057,7 @@
         <v>270</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>169</v>
@@ -7077,10 +7066,10 @@
         <v>92</v>
       </c>
       <c r="AB27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AC27" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="AD27" s="12" t="s">
         <v>346</v>
@@ -7089,7 +7078,7 @@
         <v>264</v>
       </c>
       <c r="AF27" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>91</v>
@@ -7101,7 +7090,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AK27" s="12" t="s">
         <v>344</v>
@@ -7119,10 +7108,10 @@
         <v>198</v>
       </c>
       <c r="AP27" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AQ27" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AR27" s="12" t="s">
         <v>344</v>
@@ -7131,7 +7120,7 @@
         <v>330</v>
       </c>
       <c r="AT27" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AU27" s="3" t="s">
         <v>160</v>
@@ -7143,7 +7132,7 @@
         <v>82</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AY27" s="12" t="s">
         <v>344</v>
@@ -7152,7 +7141,7 @@
         <v>270</v>
       </c>
       <c r="BA27" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="BB27" s="3" t="s">
         <v>101</v>
@@ -7161,10 +7150,10 @@
         <v>161</v>
       </c>
       <c r="BD27" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BE27" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="BF27" s="12" t="s">
         <v>344</v>
@@ -7173,7 +7162,7 @@
         <v>318</v>
       </c>
       <c r="BH27" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="BI27" s="3" t="s">
         <v>99</v>
@@ -7182,10 +7171,10 @@
         <v>136</v>
       </c>
       <c r="BK27" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BL27" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="BM27" s="12" t="s">
         <v>344</v>
@@ -7194,7 +7183,7 @@
         <v>316</v>
       </c>
       <c r="BO27" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="BP27" s="3" t="s">
         <v>91</v>
@@ -7203,33 +7192,33 @@
         <v>95</v>
       </c>
       <c r="BR27" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BS27" s="10" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:71">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="23">
         <v>46108.561006944401</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>46108.576412037</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="17">
         <v>46107</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>150</v>
@@ -7238,8 +7227,8 @@
         <v>74</v>
       </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="15" t="s">
-        <v>398</v>
+      <c r="K28" s="14" t="s">
+        <v>395</v>
       </c>
       <c r="L28" s="2">
         <v>46126</v>
@@ -7251,40 +7240,40 @@
         <v>90</v>
       </c>
       <c r="O28" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="R28" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>94</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="U28" s="3" t="s">
         <v>166</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="W28" s="12" t="s">
         <v>346</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="Z28" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>183</v>
@@ -7293,16 +7282,16 @@
         <v>119</v>
       </c>
       <c r="AC28" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AD28" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AF28" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="AD28" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="AE28" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="AF28" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="AG28" s="3" t="s">
         <v>94</v>
@@ -7314,19 +7303,19 @@
         <v>195</v>
       </c>
       <c r="AJ28" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AK28" s="12" t="s">
         <v>346</v>
       </c>
       <c r="AL28" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AM28" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AN28" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AO28" s="3" t="s">
         <v>190</v>
@@ -7335,58 +7324,58 @@
         <v>166</v>
       </c>
       <c r="AQ28" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AR28" s="12" t="s">
         <v>346</v>
       </c>
       <c r="AS28" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AT28" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AU28" s="3" t="s">
         <v>165</v>
       </c>
       <c r="AV28" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AW28" s="3" t="s">
         <v>166</v>
       </c>
       <c r="AX28" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AY28" s="12" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AZ28" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="BA28" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="BB28" s="3" t="s">
         <v>101</v>
       </c>
       <c r="BC28" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="BD28" s="3" t="s">
         <v>119</v>
       </c>
       <c r="BE28" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="BF28" s="13">
+        <v>421</v>
+      </c>
+      <c r="BF28" s="28">
         <v>45237</v>
       </c>
       <c r="BG28" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="BH28" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="BI28" s="3" t="s">
         <v>94</v>
@@ -7398,16 +7387,16 @@
         <v>119</v>
       </c>
       <c r="BL28" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="BM28" s="12" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="BN28" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="BO28" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="BP28" s="3" t="s">
         <v>158</v>
@@ -7419,30 +7408,30 @@
         <v>195</v>
       </c>
       <c r="BS28" s="10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:71">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="23">
         <v>46126.567233796297</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>46126.573217592602</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="17">
         <v>46126</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>75</v>
@@ -7451,8 +7440,8 @@
         <v>74</v>
       </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="15" t="s">
-        <v>434</v>
+      <c r="K29" s="14" t="s">
+        <v>430</v>
       </c>
       <c r="L29" s="2">
         <v>46134</v>
@@ -7464,24 +7453,24 @@
         <v>90</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="P29" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="P29" s="18" t="s">
         <v>346</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="W29" s="12" t="s">
         <v>346</v>
@@ -7492,30 +7481,30 @@
         <v>124</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AC29" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>240</v>
       </c>
       <c r="AI29" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AJ29" s="3" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AK29" s="12" t="s">
         <v>346</v>
@@ -7523,16 +7512,16 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AQ29" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AR29" s="12" t="s">
         <v>346</v>
@@ -7543,21 +7532,21 @@
         <v>99</v>
       </c>
       <c r="AV29" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AW29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AX29" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AY29" s="12" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BC29" s="3" t="s">
         <v>138</v>
@@ -7566,27 +7555,27 @@
         <v>85</v>
       </c>
       <c r="BE29" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="BF29" s="12" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="BJ29" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="BK29" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BL29" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="BM29" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
@@ -7594,36 +7583,36 @@
         <v>86</v>
       </c>
       <c r="BQ29" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BR29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="BS29" s="10" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:71">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="23">
         <v>46134.442476851902</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="23">
         <v>46134.448645833298</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="17">
         <v>46129</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>75</v>
@@ -7632,8 +7621,8 @@
         <v>150</v>
       </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="15" t="s">
-        <v>449</v>
+      <c r="K30" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="L30" s="2">
         <v>46148</v>
@@ -7645,24 +7634,24 @@
         <v>90</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="P30" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="P30" s="18" t="s">
         <v>344</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="6" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U30" s="3" t="s">
         <v>141</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="W30" s="12" t="s">
         <v>344</v>
@@ -7673,13 +7662,13 @@
         <v>103</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AB30" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AD30" s="12" t="s">
         <v>344</v>
@@ -7687,7 +7676,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AH30" s="3" t="s">
         <v>218</v>
@@ -7696,7 +7685,7 @@
         <v>137</v>
       </c>
       <c r="AJ30" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AK30" s="12" t="s">
         <v>344</v>
@@ -7713,7 +7702,7 @@
         <v>137</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AR30" s="12" t="s">
         <v>344</v>
@@ -7721,7 +7710,7 @@
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AV30" s="3" t="s">
         <v>218</v>
@@ -7730,15 +7719,15 @@
         <v>126</v>
       </c>
       <c r="AX30" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AY30" s="12" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="BC30" s="3" t="s">
         <v>111</v>
@@ -7747,7 +7736,7 @@
         <v>141</v>
       </c>
       <c r="BE30" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="BF30" s="12" t="s">
         <v>344</v>
@@ -7755,7 +7744,7 @@
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="BJ30" s="3" t="s">
         <v>218</v>
@@ -7764,7 +7753,7 @@
         <v>126</v>
       </c>
       <c r="BL30" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="BM30" s="12" t="s">
         <v>344</v>
@@ -7772,39 +7761,39 @@
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="BQ30" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="BR30" s="3" t="s">
         <v>141</v>
       </c>
       <c r="BS30" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:71">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="23">
         <v>46139.493113425902</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="23">
         <v>46139.502731481502</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="17">
         <v>46135</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>150</v>
@@ -7813,8 +7802,8 @@
         <v>75</v>
       </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="15" t="s">
-        <v>465</v>
+      <c r="K31" s="14" t="s">
+        <v>461</v>
       </c>
       <c r="L31" s="2">
         <v>46157</v>
@@ -7826,9 +7815,9 @@
         <v>90</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="P31" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="P31" s="18" t="s">
         <v>344</v>
       </c>
       <c r="Q31" s="3"/>
@@ -7843,7 +7832,7 @@
         <v>166</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="W31" s="12" t="s">
         <v>344</v>
@@ -7851,7 +7840,7 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3" t="s">
-        <v>468</v>
+        <v>124</v>
       </c>
       <c r="AA31" s="3" t="s">
         <v>95</v>
@@ -7860,7 +7849,7 @@
         <v>166</v>
       </c>
       <c r="AC31" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AD31" s="12" t="s">
         <v>344</v>
@@ -7877,9 +7866,9 @@
         <v>137</v>
       </c>
       <c r="AJ31" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="AK31" s="13">
+        <v>465</v>
+      </c>
+      <c r="AK31" s="28">
         <v>45410</v>
       </c>
       <c r="AL31" s="3"/>
@@ -7894,7 +7883,7 @@
         <v>195</v>
       </c>
       <c r="AQ31" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AR31" s="12" t="s">
         <v>344</v>
@@ -7911,7 +7900,7 @@
         <v>119</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AY31" s="12" t="s">
         <v>344</v>
@@ -7928,7 +7917,7 @@
         <v>166</v>
       </c>
       <c r="BE31" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="BF31" s="12" t="s">
         <v>344</v>
@@ -7945,7 +7934,7 @@
         <v>166</v>
       </c>
       <c r="BL31" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="BM31" s="12" t="s">
         <v>344</v>
@@ -7967,23 +7956,23 @@
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="23">
         <v>46148.717303240701</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>46148.7254398148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="17">
         <v>46146</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>150</v>
@@ -7992,11 +7981,11 @@
         <v>74</v>
       </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>477</v>
+      <c r="K32" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="L32" s="27" t="s">
+        <v>472</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>77</v>
@@ -8005,9 +7994,9 @@
         <v>90</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="P32" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="P32" s="18" t="s">
         <v>346</v>
       </c>
       <c r="Q32" s="3"/>
@@ -8016,13 +8005,13 @@
         <v>94</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="W32" s="12" t="s">
         <v>346</v>
@@ -8039,10 +8028,10 @@
         <v>166</v>
       </c>
       <c r="AC32" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AD32" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
@@ -8050,13 +8039,13 @@
         <v>234</v>
       </c>
       <c r="AH32" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="AJ32" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AK32" s="12" t="s">
         <v>346</v>
@@ -8064,7 +8053,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
       <c r="AN32" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AO32" s="3" t="s">
         <v>185</v>
@@ -8073,7 +8062,7 @@
         <v>195</v>
       </c>
       <c r="AQ32" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AR32" s="12" t="s">
         <v>346</v>
@@ -8084,13 +8073,13 @@
         <v>124</v>
       </c>
       <c r="AV32" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AW32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="AX32" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AY32" s="12" t="s">
         <v>346</v>
@@ -8101,13 +8090,13 @@
         <v>132</v>
       </c>
       <c r="BC32" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="BD32" s="3" t="s">
         <v>166</v>
       </c>
       <c r="BE32" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="BF32" s="12" t="s">
         <v>346</v>
@@ -8124,10 +8113,10 @@
         <v>119</v>
       </c>
       <c r="BL32" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="BM32" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="BN32" s="3"/>
       <c r="BO32" s="3"/>
@@ -8135,7 +8124,7 @@
         <v>101</v>
       </c>
       <c r="BQ32" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="BR32" s="3" t="s">
         <v>195</v>
@@ -8146,23 +8135,23 @@
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="23">
         <v>46154.3914814815</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="23">
         <v>46154.4005555556</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="17">
         <v>46140</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>150</v>
@@ -8171,8 +8160,8 @@
         <v>74</v>
       </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="15" t="s">
-        <v>490</v>
+      <c r="K33" s="14" t="s">
+        <v>485</v>
       </c>
       <c r="L33" s="2">
         <v>46240</v>
@@ -8184,9 +8173,9 @@
         <v>90</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="P33" s="27">
+        <v>486</v>
+      </c>
+      <c r="P33" s="26">
         <v>45410</v>
       </c>
       <c r="Q33" s="3"/>
@@ -8201,7 +8190,7 @@
         <v>166</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="W33" s="12" t="s">
         <v>344</v>
@@ -8218,7 +8207,7 @@
         <v>195</v>
       </c>
       <c r="AC33" s="3" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AD33" s="12" t="s">
         <v>344</v>
@@ -8235,9 +8224,9 @@
         <v>114</v>
       </c>
       <c r="AJ33" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="AK33" s="13">
+        <v>489</v>
+      </c>
+      <c r="AK33" s="28">
         <v>45410</v>
       </c>
       <c r="AL33" s="3"/>
@@ -8252,10 +8241,10 @@
         <v>119</v>
       </c>
       <c r="AQ33" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="AR33" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
@@ -8269,10 +8258,10 @@
         <v>166</v>
       </c>
       <c r="AX33" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="AY33" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
@@ -8286,10 +8275,10 @@
         <v>119</v>
       </c>
       <c r="BE33" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="BF33" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
@@ -8303,10 +8292,10 @@
         <v>195</v>
       </c>
       <c r="BL33" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="BM33" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="BN33" s="3"/>
       <c r="BO33" s="3"/>
@@ -8325,33 +8314,33 @@
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="23">
         <v>46167.7090509259</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>46167.737233796302</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="F34" s="18">
+        <v>496</v>
+      </c>
+      <c r="F34" s="17">
         <v>46164</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="15" t="s">
-        <v>504</v>
+      <c r="K34" s="14" t="s">
+        <v>499</v>
       </c>
       <c r="L34" s="2">
         <v>46223</v>
@@ -8363,9 +8352,9 @@
         <v>90</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="P34" s="27">
+        <v>500</v>
+      </c>
+      <c r="P34" s="26">
         <v>45227</v>
       </c>
       <c r="Q34" s="3"/>
@@ -8374,11 +8363,11 @@
         <v>145</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="W34" s="12" t="s">
         <v>346</v>
@@ -8393,10 +8382,10 @@
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
@@ -8404,13 +8393,13 @@
         <v>112</v>
       </c>
       <c r="AH34" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AI34" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AJ34" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="AK34" s="12" t="s">
         <v>346</v>
@@ -8418,7 +8407,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="AO34" s="3" t="s">
         <v>140</v>
@@ -8427,7 +8416,7 @@
         <v>195</v>
       </c>
       <c r="AQ34" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="AR34" s="12" t="s">
         <v>346</v>
@@ -8438,14 +8427,14 @@
         <v>112</v>
       </c>
       <c r="AV34" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AW34" s="3"/>
       <c r="AX34" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AY34" s="12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
@@ -8457,7 +8446,7 @@
       </c>
       <c r="BD34" s="3"/>
       <c r="BE34" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="BF34" s="12" t="s">
         <v>346</v>
@@ -8472,7 +8461,7 @@
       </c>
       <c r="BK34" s="3"/>
       <c r="BL34" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="BM34" s="12" t="s">
         <v>346</v>
@@ -8487,30 +8476,30 @@
       </c>
       <c r="BR34" s="3"/>
       <c r="BS34" s="10" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="35" spans="1:71">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <v>46176.590810185196</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>46176.598796296297</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="17">
         <v>46175</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>150</v>
@@ -8519,8 +8508,8 @@
         <v>75</v>
       </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="15" t="s">
-        <v>519</v>
+      <c r="K35" s="14" t="s">
+        <v>514</v>
       </c>
       <c r="L35" s="2">
         <v>46258</v>
@@ -8532,9 +8521,9 @@
         <v>90</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="P35" s="27">
+        <v>515</v>
+      </c>
+      <c r="P35" s="26">
         <v>45410</v>
       </c>
       <c r="Q35" s="3"/>
@@ -8549,7 +8538,7 @@
         <v>166</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="W35" s="12" t="s">
         <v>344</v>
@@ -8557,7 +8546,7 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>146</v>
@@ -8566,7 +8555,7 @@
         <v>166</v>
       </c>
       <c r="AC35" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AD35" s="12" t="s">
         <v>344</v>
@@ -8583,9 +8572,9 @@
         <v>119</v>
       </c>
       <c r="AJ35" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="AK35" s="13">
+        <v>519</v>
+      </c>
+      <c r="AK35" s="28">
         <v>45410</v>
       </c>
       <c r="AL35" s="3"/>
@@ -8600,10 +8589,10 @@
         <v>119</v>
       </c>
       <c r="AQ35" s="1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AR35" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
@@ -8617,10 +8606,10 @@
         <v>166</v>
       </c>
       <c r="AX35" s="1" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="AY35" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="3"/>
@@ -8634,10 +8623,10 @@
         <v>119</v>
       </c>
       <c r="BE35" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="BF35" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="BG35" s="3"/>
       <c r="BH35" s="3"/>
@@ -8651,10 +8640,10 @@
         <v>119</v>
       </c>
       <c r="BL35" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="BM35" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="BN35" s="3"/>
       <c r="BO35" s="3"/>
@@ -8673,10 +8662,10 @@
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="23">
         <v>46185.418587963002</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="23">
         <v>46185.425706018497</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -8685,11 +8674,11 @@
       <c r="E36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="17">
         <v>46185</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>74</v>
@@ -8698,8 +8687,8 @@
         <v>75</v>
       </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="15" t="s">
-        <v>530</v>
+      <c r="K36" s="14" t="s">
+        <v>525</v>
       </c>
       <c r="L36" s="2">
         <v>46188</v>
@@ -8711,58 +8700,58 @@
         <v>109</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>532</v>
+        <v>526</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>527</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>330</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>167</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="W36" s="12" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="X36" s="3" t="s">
         <v>323</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="Z36" s="3" t="s">
         <v>167</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AB36" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AC36" s="3" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AD36" s="12" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AE36" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AF36" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG36" s="3" t="s">
         <v>145</v>
@@ -8771,19 +8760,19 @@
         <v>122</v>
       </c>
       <c r="AI36" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AJ36" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="AK36" s="12" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AL36" s="3" t="s">
         <v>323</v>
       </c>
       <c r="AM36" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AN36" s="3" t="s">
         <v>145</v>
@@ -8792,7 +8781,7 @@
         <v>122</v>
       </c>
       <c r="AP36" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AQ36" s="1"/>
       <c r="AR36" s="12"/>
@@ -8828,10 +8817,10 @@
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="23">
         <v>46188.457777777803</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="23">
         <v>46188.458831018499</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -8840,11 +8829,11 @@
       <c r="E37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="17">
         <v>46147</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>150</v>
@@ -8853,11 +8842,11 @@
         <v>75</v>
       </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>544</v>
+      <c r="K37" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="L37" s="27" t="s">
+        <v>539</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>77</v>
@@ -8866,22 +8855,22 @@
         <v>90</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="P37" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="P37" s="18" t="s">
         <v>344</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>147</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="W37" s="12" t="s">
         <v>344</v>
@@ -8896,7 +8885,7 @@
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="AD37" s="12" t="s">
         <v>344</v>
@@ -8913,7 +8902,7 @@
         <v>126</v>
       </c>
       <c r="AJ37" s="3" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AK37" s="12" t="s">
         <v>344</v>
@@ -8930,7 +8919,7 @@
         <v>137</v>
       </c>
       <c r="AQ37" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AR37" s="12" t="s">
         <v>344</v>
@@ -8945,10 +8934,10 @@
       </c>
       <c r="AW37" s="3"/>
       <c r="AX37" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AY37" s="12" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="3"/>
@@ -8960,7 +8949,7 @@
       </c>
       <c r="BD37" s="3"/>
       <c r="BE37" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="BF37" s="12" t="s">
         <v>344</v>
@@ -8975,7 +8964,7 @@
       </c>
       <c r="BK37" s="3"/>
       <c r="BL37" s="1" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="BM37" s="12" t="s">
         <v>344</v>
@@ -8990,75 +8979,75 @@
       </c>
       <c r="BR37" s="3"/>
       <c r="BS37" s="10" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="38" spans="1:71">
       <c r="A38" s="1"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="18"/>
+      <c r="F38" s="17"/>
       <c r="G38" s="3"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="15"/>
+      <c r="K38" s="14"/>
       <c r="L38" s="2"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="28"/>
+      <c r="P38" s="18"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="6"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="29"/>
+      <c r="W38" s="12"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
-      <c r="AD38" s="29"/>
+      <c r="AD38" s="12"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
       <c r="AJ38" s="3"/>
-      <c r="AK38" s="29"/>
+      <c r="AK38" s="12"/>
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="1"/>
-      <c r="AR38" s="29"/>
+      <c r="AR38" s="12"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
       <c r="AW38" s="3"/>
       <c r="AX38" s="1"/>
-      <c r="AY38" s="29"/>
+      <c r="AY38" s="12"/>
       <c r="AZ38" s="3"/>
       <c r="BA38" s="3"/>
       <c r="BB38" s="3"/>
       <c r="BC38" s="3"/>
       <c r="BD38" s="3"/>
       <c r="BE38" s="1"/>
-      <c r="BF38" s="29"/>
+      <c r="BF38" s="12"/>
       <c r="BG38" s="3"/>
       <c r="BH38" s="3"/>
       <c r="BI38" s="3"/>
       <c r="BJ38" s="3"/>
       <c r="BK38" s="3"/>
       <c r="BL38" s="1"/>
-      <c r="BM38" s="29"/>
+      <c r="BM38" s="12"/>
       <c r="BN38" s="3"/>
       <c r="BO38" s="3"/>
       <c r="BP38" s="3"/>
@@ -9070,32 +9059,32 @@
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="23">
         <v>46226.543796296297</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="23">
         <v>46226.559270833299</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="17">
         <v>46218</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>150</v>
       </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="15"/>
+      <c r="K39" s="14"/>
       <c r="L39" s="2"/>
       <c r="M39" s="1" t="s">
         <v>77</v>
@@ -9104,10 +9093,10 @@
         <v>90</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>557</v>
+        <v>551</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>552</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -9121,10 +9110,10 @@
         <v>166</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
@@ -9138,10 +9127,10 @@
         <v>195</v>
       </c>
       <c r="AC39" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AD39" s="12" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
@@ -9155,10 +9144,10 @@
         <v>166</v>
       </c>
       <c r="AJ39" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="AK39" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
@@ -9172,10 +9161,10 @@
         <v>195</v>
       </c>
       <c r="AQ39" s="1" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="AR39" s="12" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
@@ -9189,10 +9178,10 @@
         <v>114</v>
       </c>
       <c r="AX39" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="AY39" s="12" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="3"/>
@@ -9206,10 +9195,10 @@
         <v>119</v>
       </c>
       <c r="BE39" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="BF39" s="12" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="BG39" s="3"/>
       <c r="BH39" s="3"/>
@@ -9223,15 +9212,15 @@
         <v>195</v>
       </c>
       <c r="BL39" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="BM39" s="12" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="BN39" s="3"/>
       <c r="BO39" s="3"/>
       <c r="BP39" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="BQ39" s="3" t="s">
         <v>156</v>
@@ -9245,32 +9234,32 @@
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="23">
         <v>46231.622685185197</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="23">
         <v>46231.6304282407</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="17">
         <v>46199</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="15"/>
+      <c r="K40" s="14"/>
       <c r="L40" s="2"/>
       <c r="M40" s="1" t="s">
         <v>77</v>
@@ -9279,9 +9268,9 @@
         <v>90</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="P40" s="20">
+        <v>564</v>
+      </c>
+      <c r="P40" s="19">
         <v>45858</v>
       </c>
       <c r="Q40" s="3"/>
@@ -9296,9 +9285,9 @@
         <v>166</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="W40" s="16">
+        <v>565</v>
+      </c>
+      <c r="W40" s="15">
         <v>45870</v>
       </c>
       <c r="X40" s="3"/>
@@ -9313,9 +9302,9 @@
         <v>119</v>
       </c>
       <c r="AC40" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="AD40" s="16">
+        <v>566</v>
+      </c>
+      <c r="AD40" s="15">
         <v>45870</v>
       </c>
       <c r="AE40" s="3"/>
@@ -9324,15 +9313,15 @@
         <v>86</v>
       </c>
       <c r="AH40" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AI40" s="3" t="s">
         <v>195</v>
       </c>
       <c r="AJ40" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="AK40" s="16">
+        <v>567</v>
+      </c>
+      <c r="AK40" s="15">
         <v>45845</v>
       </c>
       <c r="AL40" s="3"/>
@@ -9347,9 +9336,9 @@
         <v>166</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="AR40" s="16">
+        <v>568</v>
+      </c>
+      <c r="AR40" s="15">
         <v>45870</v>
       </c>
       <c r="AS40" s="3"/>
@@ -9364,9 +9353,9 @@
         <v>166</v>
       </c>
       <c r="AX40" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="AY40" s="16">
+        <v>569</v>
+      </c>
+      <c r="AY40" s="15">
         <v>45870</v>
       </c>
       <c r="AZ40" s="3"/>
@@ -9381,9 +9370,9 @@
         <v>195</v>
       </c>
       <c r="BE40" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="BF40" s="16">
+        <v>570</v>
+      </c>
+      <c r="BF40" s="15">
         <v>45839</v>
       </c>
       <c r="BG40" s="3"/>
@@ -9398,9 +9387,9 @@
         <v>166</v>
       </c>
       <c r="BL40" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="BM40" s="16">
+        <v>571</v>
+      </c>
+      <c r="BM40" s="30">
         <v>45870</v>
       </c>
       <c r="BN40" s="3"/>
@@ -9409,7 +9398,7 @@
         <v>145</v>
       </c>
       <c r="BQ40" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="BR40" s="3" t="s">
         <v>119</v>
@@ -9418,7 +9407,7 @@
     </row>
     <row r="41" spans="1:71">
       <c r="A41" s="5"/>
-      <c r="C41" s="24"/>
+      <c r="C41" s="23"/>
     </row>
     <row r="45" spans="1:71">
       <c r="R45" s="7"/>
@@ -9443,6 +9432,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
+    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Respons_x00e1_vel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100949757B2A3935B4A84A5374E630DBD2B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7a6d292a2f6a949c3af71fa212296ad8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="337ea2d0-885f-4217-baff-63e0aa38c74f" xmlns:ns3="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20a9319f435276383e25e3a27c1527eb" ns2:_="" ns3:_="">
     <xsd:import namespace="337ea2d0-885f-4217-baff-63e0aa38c74f"/>
@@ -9669,35 +9685,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
-    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Respons_x00e1_vel>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9705,5 +9694,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
 </file>
--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="732" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{303188DD-F5F7-46DC-B879-6AF5C4C1FA61}"/>
+  <xr:revisionPtr revIDLastSave="734" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7C45A2C-0685-4504-8031-057F7B3FB679}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1646,7 +1646,7 @@
     <t>034613c</t>
   </si>
   <si>
-    <t>12.55</t>
+    <t>5.55</t>
   </si>
   <si>
     <t>0020796</t>
@@ -5178,7 +5178,7 @@
         <v>199</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AB16" s="3" t="s">
         <v>166</v>
@@ -9432,33 +9432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
-    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Respons_x00e1_vel>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100949757B2A3935B4A84A5374E630DBD2B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7a6d292a2f6a949c3af71fa212296ad8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="337ea2d0-885f-4217-baff-63e0aa38c74f" xmlns:ns3="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20a9319f435276383e25e3a27c1527eb" ns2:_="" ns3:_="">
     <xsd:import namespace="337ea2d0-885f-4217-baff-63e0aa38c74f"/>
@@ -9685,8 +9658,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
+    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Respons_x00e1_vel>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9694,5 +9694,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="734" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7C45A2C-0685-4504-8031-057F7B3FB679}"/>
+  <xr:revisionPtr revIDLastSave="736" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07808295-86A9-4D68-BC86-7F11F2C4E5CF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="570">
   <si>
     <t>Id</t>
   </si>
@@ -645,12 +645,6 @@
   </si>
   <si>
     <t>SUL-S16</t>
-  </si>
-  <si>
-    <t>3.02</t>
-  </si>
-  <si>
-    <t>3.09</t>
   </si>
   <si>
     <t>25.3</t>
@@ -4873,7 +4867,7 @@
         <v>83</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>126</v>
@@ -4886,10 +4880,10 @@
         <v>167</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14"/>
@@ -4899,10 +4893,10 @@
         <v>145</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ14" s="1"/>
       <c r="AK14"/>
@@ -4912,7 +4906,7 @@
         <v>83</v>
       </c>
       <c r="AO14" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AP14" s="3" t="s">
         <v>126</v>
@@ -4928,7 +4922,7 @@
         <v>136</v>
       </c>
       <c r="AW14" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AX14" s="1"/>
       <c r="AY14"/>
@@ -4941,7 +4935,7 @@
         <v>106</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BE14" s="1"/>
       <c r="BF14"/>
@@ -4966,10 +4960,10 @@
         <v>144</v>
       </c>
       <c r="BR14" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="BS14" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:71">
@@ -4992,7 +4986,7 @@
         <v>45869</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>75</v>
@@ -5002,7 +4996,7 @@
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="1" t="s">
@@ -5019,7 +5013,7 @@
         <v>112</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>195</v>
@@ -5081,7 +5075,7 @@
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
       <c r="BB15" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="BC15" s="3" t="s">
         <v>115</v>
@@ -5097,7 +5091,7 @@
         <v>199</v>
       </c>
       <c r="BJ15" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BK15" s="3" t="s">
         <v>195</v>
@@ -5109,13 +5103,13 @@
         <v>83</v>
       </c>
       <c r="BQ15" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BR15" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BS15" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:71">
@@ -5138,7 +5132,7 @@
         <v>45861</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>75</v>
@@ -5148,7 +5142,7 @@
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="1" t="s">
@@ -5230,7 +5224,7 @@
         <v>101</v>
       </c>
       <c r="BC16" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BD16" s="3" t="s">
         <v>119</v>
@@ -5261,7 +5255,7 @@
         <v>119</v>
       </c>
       <c r="BS16" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:71">
@@ -5284,7 +5278,7 @@
         <v>45876</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>75</v>
@@ -5294,7 +5288,7 @@
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1" t="s">
@@ -5311,7 +5305,7 @@
         <v>167</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>137</v>
@@ -5324,7 +5318,7 @@
         <v>170</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>195</v>
@@ -5337,7 +5331,7 @@
         <v>169</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>195</v>
@@ -5383,7 +5377,7 @@
       <c r="BQ17" s="3"/>
       <c r="BR17" s="3"/>
       <c r="BS17" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:71">
@@ -5406,7 +5400,7 @@
         <v>45860</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>150</v>
@@ -5416,7 +5410,7 @@
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1" t="s">
@@ -5443,10 +5437,10 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>114</v>
@@ -5456,7 +5450,7 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>161</v>
@@ -5469,10 +5463,10 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO18" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AP18" s="3" t="s">
         <v>114</v>
@@ -5495,7 +5489,7 @@
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
       <c r="BB18" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BC18" s="3" t="s">
         <v>127</v>
@@ -5520,7 +5514,7 @@
       <c r="BN18" s="1"/>
       <c r="BO18" s="1"/>
       <c r="BP18" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="BQ18" s="3" t="s">
         <v>106</v>
@@ -5529,7 +5523,7 @@
         <v>114</v>
       </c>
       <c r="BS18" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:71">
@@ -5552,7 +5546,7 @@
         <v>45937</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>150</v>
@@ -5562,7 +5556,7 @@
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L19" s="2">
         <v>45957</v>
@@ -5581,7 +5575,7 @@
         <v>83</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U19" s="3" t="s">
         <v>119</v>
@@ -5620,7 +5614,7 @@
         <v>199</v>
       </c>
       <c r="AO19" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AP19" s="3" t="s">
         <v>114</v>
@@ -5633,7 +5627,7 @@
         <v>145</v>
       </c>
       <c r="AV19" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AW19" s="3" t="s">
         <v>119</v>
@@ -5656,7 +5650,7 @@
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
       <c r="BI19" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BJ19" s="3" t="s">
         <v>183</v>
@@ -5698,7 +5692,7 @@
         <v>45883</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>75</v>
@@ -5708,7 +5702,7 @@
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="1" t="s">
@@ -5718,11 +5712,11 @@
         <v>90</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P20" s="16"/>
       <c r="Q20" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>142</v>
@@ -5731,19 +5725,19 @@
         <v>158</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>119</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="W20" s="12"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>198</v>
@@ -5752,14 +5746,14 @@
         <v>166</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AD20"/>
       <c r="AE20" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>99</v>
@@ -5771,14 +5765,14 @@
         <v>166</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AK20"/>
       <c r="AL20" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM20" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AN20" s="3" t="s">
         <v>101</v>
@@ -5790,13 +5784,13 @@
         <v>114</v>
       </c>
       <c r="AQ20" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AR20"/>
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
       <c r="AU20" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AV20" s="3" t="s">
         <v>159</v>
@@ -5805,14 +5799,14 @@
         <v>119</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AY20"/>
       <c r="AZ20" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="BA20" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="BB20" s="3" t="s">
         <v>91</v>
@@ -5824,11 +5818,11 @@
         <v>166</v>
       </c>
       <c r="BE20" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="BF20"/>
       <c r="BG20" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="BH20" s="3" t="s">
         <v>111</v>
@@ -5837,16 +5831,16 @@
         <v>91</v>
       </c>
       <c r="BJ20" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="BK20" s="3" t="s">
         <v>166</v>
       </c>
       <c r="BL20" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="BN20" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="BO20" s="3" t="s">
         <v>185</v>
@@ -5861,7 +5855,7 @@
         <v>119</v>
       </c>
       <c r="BS20" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:71">
@@ -5884,7 +5878,7 @@
         <v>45985</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>74</v>
@@ -5894,7 +5888,7 @@
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L21" s="2">
         <v>46143</v>
@@ -5906,54 +5900,54 @@
         <v>90</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P21" s="17">
         <v>45410</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>125</v>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="W21" s="28">
         <v>45410</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>117</v>
       </c>
       <c r="AB21" s="3"/>
       <c r="AC21" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="28">
         <v>45410</v>
       </c>
       <c r="AE21" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>145</v>
@@ -5965,102 +5959,102 @@
         <v>137</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AK21" s="29">
         <v>45410</v>
       </c>
       <c r="AL21" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AM21" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AN21" s="3" t="s">
         <v>139</v>
       </c>
       <c r="AO21" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP21" s="3"/>
       <c r="AQ21" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AR21" s="29">
         <v>45410</v>
       </c>
       <c r="AS21" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AT21" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AU21" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>117</v>
       </c>
       <c r="AW21" s="3"/>
       <c r="AX21" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AY21" s="29">
         <v>45410</v>
       </c>
       <c r="AZ21" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BA21" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="BB21" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="BC21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="BD21" s="3"/>
       <c r="BE21" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="BF21" s="29">
         <v>45410</v>
       </c>
       <c r="BG21" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BH21" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="BI21" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="BJ21" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BK21" s="3"/>
       <c r="BL21" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="BM21" s="29">
         <v>45410</v>
       </c>
       <c r="BN21" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="BO21" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="BP21" s="3" t="s">
         <v>143</v>
       </c>
       <c r="BQ21" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="BR21" s="3"/>
       <c r="BS21" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:71">
@@ -6083,7 +6077,7 @@
         <v>45987</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>74</v>
@@ -6093,7 +6087,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="1" t="s">
@@ -6103,7 +6097,7 @@
         <v>90</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P22" s="17">
         <v>45411</v>
@@ -6120,7 +6114,7 @@
         <v>166</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W22" s="28">
         <v>45410</v>
@@ -6137,7 +6131,7 @@
         <v>166</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AD22" s="29">
         <v>45189</v>
@@ -6154,7 +6148,7 @@
         <v>195</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AK22" s="29">
         <v>45410</v>
@@ -6165,13 +6159,13 @@
         <v>124</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP22" s="3" t="s">
         <v>195</v>
       </c>
       <c r="AQ22" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AR22" s="29">
         <v>45410</v>
@@ -6179,7 +6173,7 @@
       <c r="AS22" s="3"/>
       <c r="AT22" s="3"/>
       <c r="AU22" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AV22" s="3" t="s">
         <v>117</v>
@@ -6188,7 +6182,7 @@
         <v>195</v>
       </c>
       <c r="AX22" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AY22" s="29">
         <v>45410</v>
@@ -6205,7 +6199,7 @@
         <v>195</v>
       </c>
       <c r="BE22" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="BF22" s="29">
         <v>45410</v>
@@ -6216,13 +6210,13 @@
         <v>99</v>
       </c>
       <c r="BJ22" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BK22" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BL22" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="BM22" s="29">
         <v>45410</v>
@@ -6233,13 +6227,13 @@
         <v>160</v>
       </c>
       <c r="BQ22" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="BR22" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BS22" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:71">
@@ -6262,7 +6256,7 @@
         <v>45847</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>75</v>
@@ -6280,32 +6274,32 @@
         <v>109</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>126</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>118</v>
@@ -6314,32 +6308,32 @@
         <v>126</v>
       </c>
       <c r="AC23" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AH23" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AJ23" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AK23" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AO23" s="3" t="s">
         <v>118</v>
@@ -6375,7 +6369,7 @@
       <c r="BQ23" s="3"/>
       <c r="BR23" s="3"/>
       <c r="BS23" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:71">
@@ -6398,7 +6392,7 @@
         <v>46035</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>74</v>
@@ -6408,7 +6402,7 @@
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L24" s="2">
         <v>46090</v>
@@ -6420,37 +6414,37 @@
         <v>90</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>79</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U24" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="W24" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="Y24" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>167</v>
@@ -6459,19 +6453,19 @@
         <v>178</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AC24" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AD24" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AE24" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AF24" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>139</v>
@@ -6480,19 +6474,19 @@
         <v>190</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AJ24" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AK24" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AL24" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AM24" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN24" s="3" t="s">
         <v>169</v>
@@ -6501,19 +6495,19 @@
         <v>111</v>
       </c>
       <c r="AP24" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="AQ24" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AR24" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS24" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AQ24" s="1" t="s">
+      <c r="AT24" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="AR24" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="AS24" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="AT24" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="AU24" s="3" t="s">
         <v>79</v>
@@ -6522,40 +6516,40 @@
         <v>190</v>
       </c>
       <c r="AW24" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="AX24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AY24" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="AZ24" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AX24" s="1" t="s">
+      <c r="BA24" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BB24" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="BC24" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="AY24" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="AZ24" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="BA24" s="3" t="s">
+      <c r="BD24" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BB24" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="BC24" s="3" t="s">
+      <c r="BE24" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="BD24" s="3" t="s">
+      <c r="BF24" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="BG24" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BE24" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="BF24" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="BG24" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="BH24" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="BI24" s="3" t="s">
         <v>79</v>
@@ -6564,31 +6558,31 @@
         <v>140</v>
       </c>
       <c r="BK24" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BL24" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="BM24" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="BN24" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BO24" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="BP24" s="3" t="s">
         <v>83</v>
       </c>
       <c r="BQ24" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BR24" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="BS24" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:71">
@@ -6611,17 +6605,17 @@
         <v>46042</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>75</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="14" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L25" s="2">
         <v>46076</v>
@@ -6633,10 +6627,10 @@
         <v>90</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P25" s="18" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -6644,21 +6638,21 @@
         <v>99</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="U25" s="3" t="s">
         <v>126</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA25" s="3" t="s">
         <v>144</v>
@@ -6667,10 +6661,10 @@
         <v>126</v>
       </c>
       <c r="AC25" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AD25" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
@@ -6684,10 +6678,10 @@
         <v>82</v>
       </c>
       <c r="AJ25" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AK25" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
@@ -6701,10 +6695,10 @@
         <v>126</v>
       </c>
       <c r="AQ25" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AR25" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AS25" s="3"/>
       <c r="AT25" s="3"/>
@@ -6718,10 +6712,10 @@
         <v>126</v>
       </c>
       <c r="AX25" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AY25" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
@@ -6735,10 +6729,10 @@
         <v>126</v>
       </c>
       <c r="BE25" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="BF25" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
@@ -6752,10 +6746,10 @@
         <v>126</v>
       </c>
       <c r="BL25" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="BM25" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
@@ -6769,7 +6763,7 @@
         <v>126</v>
       </c>
       <c r="BS25" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:71">
@@ -6783,16 +6777,16 @@
         <v>46092.499652777798</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F26" s="17">
         <v>46092</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>150</v>
@@ -6802,7 +6796,7 @@
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L26" s="2">
         <v>46100</v>
@@ -6814,16 +6808,16 @@
         <v>90</v>
       </c>
       <c r="O26" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>167</v>
@@ -6832,19 +6826,19 @@
         <v>179</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>83</v>
@@ -6856,100 +6850,100 @@
         <v>126</v>
       </c>
       <c r="AC26" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AD26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AE26" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AF26" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>139</v>
       </c>
       <c r="AH26" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AJ26" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AK26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL26" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM26" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AN26" s="3" t="s">
         <v>145</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AP26" s="3" t="s">
         <v>82</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AR26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AS26" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AT26" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AU26" s="3" t="s">
         <v>139</v>
       </c>
       <c r="AV26" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AW26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AY26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AZ26" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="BA26" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="BB26" s="3" t="s">
         <v>167</v>
       </c>
       <c r="BC26" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="BD26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="BE26" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="BF26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BG26" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="BH26" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="BI26" s="3" t="s">
         <v>79</v>
@@ -6961,28 +6955,28 @@
         <v>82</v>
       </c>
       <c r="BL26" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="BM26" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BN26" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="BO26" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="BP26" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BQ26" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="BR26" s="3" t="s">
         <v>126</v>
       </c>
       <c r="BS26" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:71">
@@ -7005,7 +6999,7 @@
         <v>46099</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>74</v>
@@ -7015,7 +7009,7 @@
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="14" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L27" s="2">
         <v>46122</v>
@@ -7027,16 +7021,16 @@
         <v>90</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>160</v>
@@ -7045,19 +7039,19 @@
         <v>106</v>
       </c>
       <c r="U27" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y27" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>169</v>
@@ -7066,19 +7060,19 @@
         <v>92</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AC27" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AD27" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AE27" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AF27" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>91</v>
@@ -7090,16 +7084,16 @@
         <v>82</v>
       </c>
       <c r="AJ27" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AK27" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL27" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AM27" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN27" s="3" t="s">
         <v>101</v>
@@ -7108,19 +7102,19 @@
         <v>198</v>
       </c>
       <c r="AP27" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AQ27" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AR27" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AS27" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AT27" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AU27" s="3" t="s">
         <v>160</v>
@@ -7132,16 +7126,16 @@
         <v>82</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AY27" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AZ27" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BA27" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB27" s="3" t="s">
         <v>101</v>
@@ -7150,19 +7144,19 @@
         <v>161</v>
       </c>
       <c r="BD27" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="BE27" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BF27" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BG27" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="BH27" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BI27" s="3" t="s">
         <v>99</v>
@@ -7171,19 +7165,19 @@
         <v>136</v>
       </c>
       <c r="BK27" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="BL27" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="BM27" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BN27" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="BO27" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="BP27" s="3" t="s">
         <v>91</v>
@@ -7192,10 +7186,10 @@
         <v>95</v>
       </c>
       <c r="BR27" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="BS27" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:71">
@@ -7209,7 +7203,7 @@
         <v>46108.576412037</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>150</v>
@@ -7218,7 +7212,7 @@
         <v>46107</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>150</v>
@@ -7228,7 +7222,7 @@
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L28" s="2">
         <v>46126</v>
@@ -7240,40 +7234,40 @@
         <v>90</v>
       </c>
       <c r="O28" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q28" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="P28" s="18" t="s">
+      <c r="R28" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>94</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="U28" s="3" t="s">
         <v>166</v>
       </c>
       <c r="V28" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="W28" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="Y28" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="W28" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="X28" s="3" t="s">
+      <c r="Z28" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z28" s="3" t="s">
-        <v>404</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>183</v>
@@ -7282,16 +7276,16 @@
         <v>119</v>
       </c>
       <c r="AC28" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="AD28" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="AE28" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="AD28" s="12" t="s">
+      <c r="AF28" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="AE28" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="AF28" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="AG28" s="3" t="s">
         <v>94</v>
@@ -7303,19 +7297,19 @@
         <v>195</v>
       </c>
       <c r="AJ28" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="AK28" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AM28" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AK28" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="AL28" s="3" t="s">
+      <c r="AN28" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="AM28" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="AN28" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="AO28" s="3" t="s">
         <v>190</v>
@@ -7324,58 +7318,58 @@
         <v>166</v>
       </c>
       <c r="AQ28" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AR28" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="AS28" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="AT28" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="AR28" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="AS28" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="AT28" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="AU28" s="3" t="s">
         <v>165</v>
       </c>
       <c r="AV28" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AW28" s="3" t="s">
         <v>166</v>
       </c>
       <c r="AX28" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="AY28" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="AZ28" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BA28" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="AY28" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="AZ28" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="BA28" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="BB28" s="3" t="s">
         <v>101</v>
       </c>
       <c r="BC28" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BD28" s="3" t="s">
         <v>119</v>
       </c>
       <c r="BE28" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BF28" s="28">
         <v>45237</v>
       </c>
       <c r="BG28" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BH28" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BI28" s="3" t="s">
         <v>94</v>
@@ -7387,16 +7381,16 @@
         <v>119</v>
       </c>
       <c r="BL28" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="BM28" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="BN28" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="BO28" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="BM28" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="BN28" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="BO28" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="BP28" s="3" t="s">
         <v>158</v>
@@ -7408,7 +7402,7 @@
         <v>195</v>
       </c>
       <c r="BS28" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" spans="1:71">
@@ -7422,7 +7416,7 @@
         <v>46126.573217592602</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>75</v>
@@ -7431,7 +7425,7 @@
         <v>46126</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>75</v>
@@ -7441,7 +7435,7 @@
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L29" s="2">
         <v>46134</v>
@@ -7453,27 +7447,27 @@
         <v>90</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P29" s="18" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -7481,50 +7475,50 @@
         <v>124</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AC29" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AH29" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AI29" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AJ29" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AK29" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AQ29" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AR29" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AS29" s="3"/>
       <c r="AT29" s="3"/>
@@ -7532,21 +7526,21 @@
         <v>99</v>
       </c>
       <c r="AV29" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AW29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AX29" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AY29" s="12" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="BC29" s="3" t="s">
         <v>138</v>
@@ -7555,27 +7549,27 @@
         <v>85</v>
       </c>
       <c r="BE29" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="BF29" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="BJ29" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BK29" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="BL29" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="BM29" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
@@ -7583,13 +7577,13 @@
         <v>86</v>
       </c>
       <c r="BQ29" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="BR29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="BS29" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:71">
@@ -7603,7 +7597,7 @@
         <v>46134.448645833298</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>75</v>
@@ -7612,7 +7606,7 @@
         <v>46129</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>75</v>
@@ -7622,7 +7616,7 @@
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L30" s="2">
         <v>46148</v>
@@ -7634,27 +7628,27 @@
         <v>90</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="U30" s="3" t="s">
         <v>141</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
@@ -7662,33 +7656,33 @@
         <v>103</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AB30" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AD30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AH30" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AI30" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AJ30" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AK30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
@@ -7696,38 +7690,38 @@
         <v>103</v>
       </c>
       <c r="AO30" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP30" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AR30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AV30" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AW30" s="3" t="s">
         <v>126</v>
       </c>
       <c r="AX30" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AY30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="BC30" s="3" t="s">
         <v>111</v>
@@ -7736,41 +7730,41 @@
         <v>141</v>
       </c>
       <c r="BE30" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="BF30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BJ30" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BK30" s="3" t="s">
         <v>126</v>
       </c>
       <c r="BL30" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="BM30" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="BQ30" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="BR30" s="3" t="s">
         <v>141</v>
       </c>
       <c r="BS30" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:71">
@@ -7784,7 +7778,7 @@
         <v>46139.502731481502</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>150</v>
@@ -7793,7 +7787,7 @@
         <v>46135</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>150</v>
@@ -7803,7 +7797,7 @@
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="14" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L31" s="2">
         <v>46157</v>
@@ -7815,10 +7809,10 @@
         <v>90</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -7832,10 +7826,10 @@
         <v>166</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
@@ -7849,10 +7843,10 @@
         <v>166</v>
       </c>
       <c r="AC31" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AD31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
@@ -7866,7 +7860,7 @@
         <v>137</v>
       </c>
       <c r="AJ31" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AK31" s="28">
         <v>45410</v>
@@ -7877,16 +7871,16 @@
         <v>91</v>
       </c>
       <c r="AO31" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AP31" s="3" t="s">
         <v>195</v>
       </c>
       <c r="AQ31" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AR31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AS31" s="3"/>
       <c r="AT31" s="3"/>
@@ -7900,10 +7894,10 @@
         <v>119</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AY31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
@@ -7917,10 +7911,10 @@
         <v>166</v>
       </c>
       <c r="BE31" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="BF31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BG31" s="3"/>
       <c r="BH31" s="3"/>
@@ -7928,16 +7922,16 @@
         <v>158</v>
       </c>
       <c r="BJ31" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BK31" s="3" t="s">
         <v>166</v>
       </c>
       <c r="BL31" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="BM31" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BN31" s="3"/>
       <c r="BO31" s="3"/>
@@ -7963,7 +7957,7 @@
         <v>46148.7254398148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>150</v>
@@ -7972,7 +7966,7 @@
         <v>46146</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>150</v>
@@ -7982,10 +7976,10 @@
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>77</v>
@@ -7994,10 +7988,10 @@
         <v>90</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P32" s="18" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -8005,16 +7999,16 @@
         <v>94</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -8028,32 +8022,32 @@
         <v>166</v>
       </c>
       <c r="AC32" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AD32" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AH32" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="AJ32" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AK32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
       <c r="AN32" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AO32" s="3" t="s">
         <v>185</v>
@@ -8062,10 +8056,10 @@
         <v>195</v>
       </c>
       <c r="AQ32" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AR32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AS32" s="3"/>
       <c r="AT32" s="3"/>
@@ -8073,16 +8067,16 @@
         <v>124</v>
       </c>
       <c r="AV32" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AW32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="AX32" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AY32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="3"/>
@@ -8090,33 +8084,33 @@
         <v>132</v>
       </c>
       <c r="BC32" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="BD32" s="3" t="s">
         <v>166</v>
       </c>
       <c r="BE32" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="BF32" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BG32" s="3"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="BJ32" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BK32" s="3" t="s">
         <v>119</v>
       </c>
       <c r="BL32" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="BM32" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="BN32" s="3"/>
       <c r="BO32" s="3"/>
@@ -8124,7 +8118,7 @@
         <v>101</v>
       </c>
       <c r="BQ32" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="BR32" s="3" t="s">
         <v>195</v>
@@ -8142,7 +8136,7 @@
         <v>46154.4005555556</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>150</v>
@@ -8151,7 +8145,7 @@
         <v>46140</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>150</v>
@@ -8161,7 +8155,7 @@
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L33" s="2">
         <v>46240</v>
@@ -8173,7 +8167,7 @@
         <v>90</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P33" s="26">
         <v>45410</v>
@@ -8190,10 +8184,10 @@
         <v>166</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -8207,10 +8201,10 @@
         <v>195</v>
       </c>
       <c r="AC33" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AD33" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
@@ -8224,7 +8218,7 @@
         <v>114</v>
       </c>
       <c r="AJ33" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AK33" s="28">
         <v>45410</v>
@@ -8241,10 +8235,10 @@
         <v>119</v>
       </c>
       <c r="AQ33" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AR33" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
@@ -8252,16 +8246,16 @@
         <v>91</v>
       </c>
       <c r="AV33" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AW33" s="3" t="s">
         <v>166</v>
       </c>
       <c r="AX33" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AY33" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
@@ -8275,10 +8269,10 @@
         <v>119</v>
       </c>
       <c r="BE33" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="BF33" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
@@ -8286,16 +8280,16 @@
         <v>165</v>
       </c>
       <c r="BJ33" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="BK33" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BL33" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="BM33" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="BN33" s="3"/>
       <c r="BO33" s="3"/>
@@ -8321,26 +8315,26 @@
         <v>46167.737233796302</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F34" s="17">
         <v>46164</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="14" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L34" s="2">
         <v>46223</v>
@@ -8352,7 +8346,7 @@
         <v>90</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P34" s="26">
         <v>45227</v>
@@ -8363,14 +8357,14 @@
         <v>145</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="W34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -8382,10 +8376,10 @@
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
@@ -8393,21 +8387,21 @@
         <v>112</v>
       </c>
       <c r="AH34" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AI34" s="3" t="s">
         <v>137</v>
       </c>
       <c r="AJ34" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AK34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AO34" s="3" t="s">
         <v>140</v>
@@ -8416,10 +8410,10 @@
         <v>195</v>
       </c>
       <c r="AQ34" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AR34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
@@ -8427,14 +8421,14 @@
         <v>112</v>
       </c>
       <c r="AV34" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AW34" s="3"/>
       <c r="AX34" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AY34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
@@ -8442,14 +8436,14 @@
         <v>145</v>
       </c>
       <c r="BC34" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="BD34" s="3"/>
       <c r="BE34" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="BF34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BG34" s="3"/>
       <c r="BH34" s="3"/>
@@ -8461,10 +8455,10 @@
       </c>
       <c r="BK34" s="3"/>
       <c r="BL34" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="BM34" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BN34" s="3"/>
       <c r="BO34" s="3"/>
@@ -8476,7 +8470,7 @@
       </c>
       <c r="BR34" s="3"/>
       <c r="BS34" s="10" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35" spans="1:71">
@@ -8490,7 +8484,7 @@
         <v>46176.598796296297</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>150</v>
@@ -8499,7 +8493,7 @@
         <v>46175</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>150</v>
@@ -8509,7 +8503,7 @@
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L35" s="2">
         <v>46258</v>
@@ -8521,7 +8515,7 @@
         <v>90</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P35" s="26">
         <v>45410</v>
@@ -8532,21 +8526,21 @@
         <v>132</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>166</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="W35" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>146</v>
@@ -8555,10 +8549,10 @@
         <v>166</v>
       </c>
       <c r="AC35" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AD35" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
@@ -8572,7 +8566,7 @@
         <v>119</v>
       </c>
       <c r="AJ35" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AK35" s="28">
         <v>45410</v>
@@ -8589,10 +8583,10 @@
         <v>119</v>
       </c>
       <c r="AQ35" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AR35" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
@@ -8606,10 +8600,10 @@
         <v>166</v>
       </c>
       <c r="AX35" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AY35" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="3"/>
@@ -8623,10 +8617,10 @@
         <v>119</v>
       </c>
       <c r="BE35" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="BF35" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="BG35" s="3"/>
       <c r="BH35" s="3"/>
@@ -8634,16 +8628,16 @@
         <v>124</v>
       </c>
       <c r="BJ35" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BK35" s="3" t="s">
         <v>119</v>
       </c>
       <c r="BL35" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="BM35" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="BN35" s="3"/>
       <c r="BO35" s="3"/>
@@ -8651,7 +8645,7 @@
         <v>158</v>
       </c>
       <c r="BQ35" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="BR35" s="3" t="s">
         <v>166</v>
@@ -8678,7 +8672,7 @@
         <v>46185</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>74</v>
@@ -8688,7 +8682,7 @@
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L36" s="2">
         <v>46188</v>
@@ -8700,58 +8694,58 @@
         <v>109</v>
       </c>
       <c r="O36" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="R36" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="P36" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>167</v>
       </c>
       <c r="T36" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="W36" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y36" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="W36" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="Z36" s="3" t="s">
         <v>167</v>
       </c>
       <c r="AA36" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="AB36" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="AC36" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="AD36" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="AE36" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="AF36" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="AB36" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="AC36" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="AD36" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="AE36" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="AF36" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="AG36" s="3" t="s">
         <v>145</v>
@@ -8760,19 +8754,19 @@
         <v>122</v>
       </c>
       <c r="AI36" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AJ36" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AK36" s="12" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AL36" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AM36" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AN36" s="3" t="s">
         <v>145</v>
@@ -8781,7 +8775,7 @@
         <v>122</v>
       </c>
       <c r="AP36" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AQ36" s="1"/>
       <c r="AR36" s="12"/>
@@ -8833,7 +8827,7 @@
         <v>46147</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>150</v>
@@ -8843,10 +8837,10 @@
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="14" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="L37" s="27" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>77</v>
@@ -8855,25 +8849,25 @@
         <v>90</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>147</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="W37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
@@ -8881,14 +8875,14 @@
         <v>94</v>
       </c>
       <c r="AA37" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AD37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
@@ -8902,10 +8896,10 @@
         <v>126</v>
       </c>
       <c r="AJ37" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AK37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
@@ -8919,10 +8913,10 @@
         <v>137</v>
       </c>
       <c r="AQ37" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AR37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
@@ -8934,10 +8928,10 @@
       </c>
       <c r="AW37" s="3"/>
       <c r="AX37" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AY37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="3"/>
@@ -8949,10 +8943,10 @@
       </c>
       <c r="BD37" s="3"/>
       <c r="BE37" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="BF37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BG37" s="3"/>
       <c r="BH37" s="3"/>
@@ -8964,10 +8958,10 @@
       </c>
       <c r="BK37" s="3"/>
       <c r="BL37" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="BM37" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BN37" s="3"/>
       <c r="BO37" s="3"/>
@@ -8979,7 +8973,7 @@
       </c>
       <c r="BR37" s="3"/>
       <c r="BS37" s="10" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="38" spans="1:71">
@@ -9066,7 +9060,7 @@
         <v>46226.559270833299</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>150</v>
@@ -9075,10 +9069,10 @@
         <v>46218</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>150</v>
@@ -9093,10 +9087,10 @@
         <v>90</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P39" s="18" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -9110,10 +9104,10 @@
         <v>166</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
@@ -9127,10 +9121,10 @@
         <v>195</v>
       </c>
       <c r="AC39" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AD39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
@@ -9144,10 +9138,10 @@
         <v>166</v>
       </c>
       <c r="AJ39" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AK39" s="12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
@@ -9161,10 +9155,10 @@
         <v>195</v>
       </c>
       <c r="AQ39" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="AR39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
@@ -9178,10 +9172,10 @@
         <v>114</v>
       </c>
       <c r="AX39" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AY39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="3"/>
@@ -9195,10 +9189,10 @@
         <v>119</v>
       </c>
       <c r="BE39" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="BF39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="BG39" s="3"/>
       <c r="BH39" s="3"/>
@@ -9206,21 +9200,21 @@
         <v>199</v>
       </c>
       <c r="BJ39" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BK39" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BL39" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="BM39" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="BN39" s="3"/>
       <c r="BO39" s="3"/>
       <c r="BP39" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="BQ39" s="3" t="s">
         <v>156</v>
@@ -9241,7 +9235,7 @@
         <v>46231.6304282407</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>150</v>
@@ -9250,13 +9244,13 @@
         <v>46199</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>150</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="14"/>
@@ -9268,7 +9262,7 @@
         <v>90</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="P40" s="19">
         <v>45858</v>
@@ -9279,13 +9273,13 @@
         <v>145</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>166</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="W40" s="15">
         <v>45870</v>
@@ -9296,13 +9290,13 @@
         <v>167</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AB40" s="3" t="s">
         <v>119</v>
       </c>
       <c r="AC40" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AD40" s="15">
         <v>45870</v>
@@ -9313,13 +9307,13 @@
         <v>86</v>
       </c>
       <c r="AH40" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AI40" s="3" t="s">
         <v>195</v>
       </c>
       <c r="AJ40" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AK40" s="15">
         <v>45845</v>
@@ -9330,13 +9324,13 @@
         <v>139</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AP40" s="3" t="s">
         <v>166</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AR40" s="15">
         <v>45870</v>
@@ -9353,7 +9347,7 @@
         <v>166</v>
       </c>
       <c r="AX40" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AY40" s="15">
         <v>45870</v>
@@ -9364,13 +9358,13 @@
         <v>145</v>
       </c>
       <c r="BC40" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="BD40" s="3" t="s">
         <v>195</v>
       </c>
       <c r="BE40" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="BF40" s="15">
         <v>45839</v>
@@ -9381,13 +9375,13 @@
         <v>83</v>
       </c>
       <c r="BJ40" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BK40" s="3" t="s">
         <v>166</v>
       </c>
       <c r="BL40" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="BM40" s="30">
         <v>45870</v>
@@ -9398,7 +9392,7 @@
         <v>145</v>
       </c>
       <c r="BQ40" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="BR40" s="3" t="s">
         <v>119</v>
@@ -9432,6 +9426,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
+    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Respons_x00e1_vel>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100949757B2A3935B4A84A5374E630DBD2B" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7a6d292a2f6a949c3af71fa212296ad8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="337ea2d0-885f-4217-baff-63e0aa38c74f" xmlns:ns3="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20a9319f435276383e25e3a27c1527eb" ns2:_="" ns3:_="">
     <xsd:import namespace="337ea2d0-885f-4217-baff-63e0aa38c74f"/>
@@ -9658,35 +9679,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="88b5053f-70bf-4e85-aff7-c22fa84ac4ca" xsi:nil="true"/>
-    <Respons_x00e1_vel xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Respons_x00e1_vel>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9694,5 +9688,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53916EA2-407A-40AC-B2E2-3247788E9B77}"/>
 </file>
--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="736" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07808295-86A9-4D68-BC86-7F11F2C4E5CF}"/>
+  <xr:revisionPtr revIDLastSave="741" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C1AFF8-C36E-4141-A84A-696BF3D0E8B5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="570">
   <si>
     <t>Id</t>
   </si>
@@ -2057,7 +2057,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -2076,7 +2076,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -3599,7 +3599,9 @@
       <c r="I5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="14"/>
+      <c r="K5" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1" t="s">
         <v>77</v>
@@ -3700,7 +3702,9 @@
       <c r="I6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="14"/>
+      <c r="K6" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="1" t="s">
         <v>77</v>
@@ -3977,7 +3981,9 @@
         <v>75</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="14"/>
+      <c r="K8" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="1" t="s">
         <v>77</v>
@@ -9426,6 +9432,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
@@ -9441,15 +9456,6 @@
     </Respons_x00e1_vel>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9680,11 +9686,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="741" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C1AFF8-C36E-4141-A84A-696BF3D0E8B5}"/>
+  <xr:revisionPtr revIDLastSave="749" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C02D59D-3251-4AFE-A741-F1880C75073C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="572">
   <si>
     <t>Id</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>Relatório</t>
+  </si>
+  <si>
+    <t>Retornou ao Galpão</t>
+  </si>
+  <si>
+    <t>Data de Retorno</t>
   </si>
   <si>
     <t>felipe.freitas@telematica.com.br</t>
@@ -1876,7 +1882,13 @@
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="75">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -2116,500 +2128,502 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:BS40" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
-  <autoFilter ref="A1:BS40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="71">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:BU40" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
+  <autoFilter ref="A1:BU40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="73">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="72">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora de início" dataDxfId="69">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora de início" dataDxfId="71">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora de conclusão" dataDxfId="68">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hora de conclusão" dataDxfId="70">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="67">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="69">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="66">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="68">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data da Desufatação" dataDxfId="65">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Data da Desufatação" dataDxfId="67">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1c0deda92be540d18d6fe0895f1d2b5f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Número de Série do Banco de Baterias" dataDxfId="64">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Número de Série do Banco de Baterias" dataDxfId="66">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r95ead006d4f146f1ad112ba2a62944b3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nome do Tecnico Responsável Montagem:" dataDxfId="63">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nome do Tecnico Responsável Montagem:" dataDxfId="65">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8504b0f8dbd748e293216952bd42565c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Nome do Tecnico Responsável Conferência:" dataDxfId="62">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Nome do Tecnico Responsável Conferência:" dataDxfId="64">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r93d08240a6774336a51924bca6ba98ec"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="71" xr3:uid="{B6D50E16-064C-45B5-B2D8-E521B59679AE}" name="Coluna1" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAG da Sirene" dataDxfId="60">
+    <tableColumn id="71" xr3:uid="{B6D50E16-064C-45B5-B2D8-E521B59679AE}" name="Coluna1" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAG da Sirene" dataDxfId="62">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc09291c973064723a307896895c0b5bc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{2815341C-41F9-4CC4-B8C4-32C0E27D3CA8}" name="Data Implatação" dataDxfId="59">
+    <tableColumn id="62" xr3:uid="{2815341C-41F9-4CC4-B8C4-32C0E27D3CA8}" name="Data Implatação" dataDxfId="61">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r204f54b9aa9349e89f5219d164327395"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Esse Banco já foi Desufatado?" dataDxfId="58">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Esse Banco já foi Desufatado?" dataDxfId="60">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r10a1abfade8043b8afc84703374009b3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Versão do Banco" dataDxfId="57">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Versão do Banco" dataDxfId="59">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r52d1048444004cc9a3e02afcda9dddf1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Numero de série Bateria 1:" dataDxfId="56">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Numero de série Bateria 1:" dataDxfId="58">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r51563a74be1d420a93bb38fb5b30222c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="63" xr3:uid="{4CDC1813-59EF-4897-A037-47239B189154}" name="Data de fabricação Bateria 1:" dataDxfId="55">
+    <tableColumn id="63" xr3:uid="{4CDC1813-59EF-4897-A037-47239B189154}" name="Data de fabricação Bateria 1:" dataDxfId="57">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r38319cf72731492c87c02e6205945cf6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tensão Antes Bateria 1:" dataDxfId="54">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Tensão Antes Bateria 1:" dataDxfId="56">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="raf9b499e8bf94e0e9c5f4fafd7fc2f8c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Resistência Antes Bateria 1:" dataDxfId="53">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Resistência Antes Bateria 1:" dataDxfId="55">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcf25f8964c7947ddb7f920c8a7a61437"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Tensão Depois Bateria 1:" dataDxfId="52">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Tensão Depois Bateria 1:" dataDxfId="54">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rae69a1c6266842d69c1e1d63401bfc21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Resistência Depois Bateria 1:" dataDxfId="51">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Resistência Depois Bateria 1:" dataDxfId="53">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r844ddcc7349d4a16bee01df73654e9de"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Temperatura Bateria 1:" dataDxfId="50">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Temperatura Bateria 1:" dataDxfId="52">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r48d5bc1d96234f15b70d29ab92479c0b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Numero de série Bateria 2:" dataDxfId="49">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Numero de série Bateria 2:" dataDxfId="51">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r16a365f1e0044871b1f84ec1b76e6195"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="64" xr3:uid="{BA0EDF2C-71BC-42F5-85C7-6FE20AEDC5BB}" name="Data de fabricação Bateria 2:" dataDxfId="48">
+    <tableColumn id="64" xr3:uid="{BA0EDF2C-71BC-42F5-85C7-6FE20AEDC5BB}" name="Data de fabricação Bateria 2:" dataDxfId="50">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra0d9095722e249cca21255b3597c4ba4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Tensão Antes Bateria 2:" dataDxfId="47">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Tensão Antes Bateria 2:" dataDxfId="49">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5527069abf114b25917277da82d4562b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Resistência Antes Bateria 2:" dataDxfId="46">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Resistência Antes Bateria 2:" dataDxfId="48">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r66d188a0da704b018835d10c6b01b200"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Tensão Depois Bateria 2:" dataDxfId="45">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Tensão Depois Bateria 2:" dataDxfId="47">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf40a62599707420c97304d6e2def3ae3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Resistência Depois Bateria 2:" dataDxfId="44">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Resistência Depois Bateria 2:" dataDxfId="46">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf3476cdc8537492ba1915f9e060be67a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Temperatura Bateria 2:" dataDxfId="43">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Temperatura Bateria 2:" dataDxfId="45">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1e5b72c937de405e80b19289cb4b3066"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Numero de série Bateria 3:" dataDxfId="42">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Numero de série Bateria 3:" dataDxfId="44">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0b9d2ec1daa048f1a0dd98a54d700bde"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="65" xr3:uid="{C61F8550-A22D-4E8D-AF68-CD9903D23FE3}" name="Data de fabricação Bateria 3:" dataDxfId="41">
+    <tableColumn id="65" xr3:uid="{C61F8550-A22D-4E8D-AF68-CD9903D23FE3}" name="Data de fabricação Bateria 3:" dataDxfId="43">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r84ea2f487fdb4e1ea0442b6d190b479a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Tensão Antes Bateria 3:" dataDxfId="40">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Tensão Antes Bateria 3:" dataDxfId="42">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3cad5c2120ea405aabb6d0acbe5012a7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Resistência Antes Bateria 3:" dataDxfId="39">
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Resistência Antes Bateria 3:" dataDxfId="41">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="raa4efd1f1a7f49378e378fcf734af9b5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Tensão Depois Bateria 3:" dataDxfId="38">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Tensão Depois Bateria 3:" dataDxfId="40">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r39581adc24cd4f859757ea869a6bb890"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Resistência Depois Bateria 3:" dataDxfId="37">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Resistência Depois Bateria 3:" dataDxfId="39">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r55561888f2d042f2a4b7c2a4f18128f3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Temperatura Bateria 3:" dataDxfId="36">
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Temperatura Bateria 3:" dataDxfId="38">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0feddd03f38c4065a2167a991a59cd0a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Numero de série Bateria 4:" dataDxfId="35">
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Numero de série Bateria 4:" dataDxfId="37">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r4b17b73f1fb847e09aa3223626ffd6a8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="66" xr3:uid="{B06DA19F-C1F4-456A-B2CF-1F7C7A3083E4}" name="Data de fabricação Bateria 4:" dataDxfId="34">
+    <tableColumn id="66" xr3:uid="{B06DA19F-C1F4-456A-B2CF-1F7C7A3083E4}" name="Data de fabricação Bateria 4:" dataDxfId="36">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r4fdac2e5840c45c0a14e052b2fb595d6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Tensão Antes Bateria 4:" dataDxfId="33">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Tensão Antes Bateria 4:" dataDxfId="35">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5b49393a86e444ada49d1ba6eb3ca471"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Resistência Antes Bateria 4:" dataDxfId="32">
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Resistência Antes Bateria 4:" dataDxfId="34">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r62c0762d9a8b4a39b2a10cc5ca1a189e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Tensão Depois Bateria 4:" dataDxfId="31">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Tensão Depois Bateria 4:" dataDxfId="33">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r00c79836e3e54a0e924a180e7cd5ce50"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Resistência Depois Bateria 4:" dataDxfId="30">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Resistência Depois Bateria 4:" dataDxfId="32">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r329cb65db80f411aa77f3ee96abf9e8d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Temperatura Bateria 4:" dataDxfId="29">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Temperatura Bateria 4:" dataDxfId="31">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra1566b3f6dba470581d0bf1fe1e23fb8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Numero de série Bateria 5:" dataDxfId="28">
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Numero de série Bateria 5:" dataDxfId="30">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5943e3c8bd9d4e5a9e4453b019feb330"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="67" xr3:uid="{E6B8B996-5660-45CD-83BE-10D8F448AE39}" name="Data de fabricação Bateria 5:" dataDxfId="27">
+    <tableColumn id="67" xr3:uid="{E6B8B996-5660-45CD-83BE-10D8F448AE39}" name="Data de fabricação Bateria 5:" dataDxfId="29">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r82ac1f391f604e1cb5241ad92bb6bc41"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Tensão Antes Bateria 5:" dataDxfId="26">
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Tensão Antes Bateria 5:" dataDxfId="28">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfe5e8b76ac154809afe5a133c224c57e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Resistência Antes Bateria 5:" dataDxfId="25">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Resistência Antes Bateria 5:" dataDxfId="27">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r60c54fc9436b4e0aaeaced2081bc0ca0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Tensão Depois Bateria 5:" dataDxfId="24">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Tensão Depois Bateria 5:" dataDxfId="26">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8be0158209bd4e08a286d23e31a91266"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Resistência Depois Bateria 5:" dataDxfId="23">
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Resistência Depois Bateria 5:" dataDxfId="25">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r156061bdef7e47299f2c8ad8cdac5b55"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Temperatura Bateria 5:" dataDxfId="22">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Temperatura Bateria 5:" dataDxfId="24">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6d0c867df2384033a534f66e7e561675"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Numero de série Bateria 6:" dataDxfId="21">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Numero de série Bateria 6:" dataDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd0374e15e94844b5af4c3daa09a55b83"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="68" xr3:uid="{523A24C3-8790-48D0-B26A-7399B8C598FF}" name="Data de fabricação Bateria 6:" dataDxfId="20">
+    <tableColumn id="68" xr3:uid="{523A24C3-8790-48D0-B26A-7399B8C598FF}" name="Data de fabricação Bateria 6:" dataDxfId="22">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc8407952130c4b7d841246228ee12601"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Tensão Antes Bateria 6:" dataDxfId="19">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Tensão Antes Bateria 6:" dataDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3c0b6dc4defe4b81b724187be86fcf96"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Resistência Antes Bateria 6:" dataDxfId="18">
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Resistência Antes Bateria 6:" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r097a25fc1c484603a22117a6e6715964"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Tensão Depois Bateria 6:" dataDxfId="17">
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Tensão Depois Bateria 6:" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r2db00b94bb0f486fad3129a871e88341"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Resistência Depois Bateria 6:" dataDxfId="16">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Resistência Depois Bateria 6:" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0274a0134ac8492ea40118f73e29056c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Temperatura Bateria 6:" dataDxfId="15">
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Temperatura Bateria 6:" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r23ef986a49494a9b9dad800e6b6fee0e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Numero de série Bateria 7:" dataDxfId="14">
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Numero de série Bateria 7:" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf33030c9960943e6970942502710c58f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="69" xr3:uid="{BDC7101C-4694-4CE2-A656-63E2BAE10979}" name="Data de fabricação Bateria 7:" dataDxfId="13">
+    <tableColumn id="69" xr3:uid="{BDC7101C-4694-4CE2-A656-63E2BAE10979}" name="Data de fabricação Bateria 7:" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7088c8628ac945979fd0ef4f4106e74b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Tensão Antes Bateria 7:" dataDxfId="12">
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Tensão Antes Bateria 7:" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="recb188e6c7094d089458fbc5da66e497"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Resistência Antes Bateria 7:" dataDxfId="11">
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Resistência Antes Bateria 7:" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8b85621666c84caeb160d151ba72009b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Tensão Depois Bateria 7:" dataDxfId="10">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Tensão Depois Bateria 7:" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rde8a5500e67c44ecaa3cf89f5b86c4a5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Resistência Depois Bateria 7:" dataDxfId="9">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Resistência Depois Bateria 7:" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r82636511a9584d05bd5ef6a3c181746e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Temperatura Bateria 7:" dataDxfId="8">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Temperatura Bateria 7:" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc88acaa60b194b58888189010f173804"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Numero de série Bateria 8:" dataDxfId="7">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Numero de série Bateria 8:" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re9819a2065474dc5ae80b145dc767617"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="70" xr3:uid="{7519E37F-BE03-4ADA-ACFF-663F06EA51FE}" name="Data de fabricação Bateria 8:" dataDxfId="6">
+    <tableColumn id="70" xr3:uid="{7519E37F-BE03-4ADA-ACFF-663F06EA51FE}" name="Data de fabricação Bateria 8:" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rad5e797cf148498386e5ad160c2c2481"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Tensão Antes Bateria 8:" dataDxfId="5">
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Tensão Antes Bateria 8:" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9fde5990803b4bd9942842e20d595faa"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Resistência Antes Bateria 8:" dataDxfId="4">
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Resistência Antes Bateria 8:" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc1e28d188c774ea981729a75fffdaf1b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Tensão Depois Bateria 8:" dataDxfId="3">
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Tensão Depois Bateria 8:" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa0ccc2750684957912b12da49571b8c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Resistência Depois Bateria 8:" dataDxfId="2">
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Resistência Depois Bateria 8:" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r4c782befacb54f8cba3c657ed85b1f21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Temperatura Bateria 8:" dataDxfId="1">
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Temperatura Bateria 8:" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfbc9f481cb72492bb6f3cf66d6b77a5e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Relatório" dataDxfId="0">
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Relatório" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r601e51ad50f74d06ba9909b7378530f8"/>
         </ext>
       </extLst>
     </tableColumn>
+    <tableColumn id="72" xr3:uid="{AF06F6C5-C040-4D40-B10C-245A06BFB435}" name="Retornou ao Galpão" dataDxfId="1"/>
+    <tableColumn id="73" xr3:uid="{DB566814-E4C8-4FBF-9A2C-7C3F71DB31DE}" name="Data de Retorno" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2988,7 +3002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS48"/>
+  <dimension ref="A1:BU48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
@@ -3030,9 +3044,11 @@
     <col min="65" max="65" width="19" customWidth="1"/>
     <col min="70" max="70" width="11.42578125" customWidth="1"/>
     <col min="71" max="71" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="73.7109375" customWidth="1"/>
+    <col min="73" max="73" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="21" customFormat="1" ht="40.5" customHeight="1">
+    <row r="1" spans="1:73" s="21" customFormat="1" ht="40.5" customHeight="1">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -3246,8 +3262,14 @@
       <c r="BS1" s="21" t="s">
         <v>70</v>
       </c>
+      <c r="BT1" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="21" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="1:71" s="1" customFormat="1">
+    <row r="2" spans="1:73" s="1" customFormat="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3258,79 +3280,79 @@
         <v>45901.745532407411</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="17">
         <v>45708</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P2" s="16"/>
       <c r="S2" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U2" s="3">
         <v>27</v>
       </c>
       <c r="W2"/>
       <c r="Z2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AD2"/>
       <c r="AG2" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK2"/>
       <c r="AN2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AO2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP2" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="AR2"/>
       <c r="AY2"/>
       <c r="BF2"/>
       <c r="BM2"/>
     </row>
-    <row r="3" spans="1:71" s="1" customFormat="1">
+    <row r="3" spans="1:73" s="1" customFormat="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3341,115 +3363,115 @@
         <v>45901.750150462998</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="17">
         <v>45714</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P3" s="16"/>
       <c r="S3" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W3"/>
       <c r="Z3" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AD3"/>
       <c r="AG3" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK3"/>
       <c r="AN3" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AR3"/>
       <c r="AU3" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AV3" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AW3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AY3"/>
       <c r="BB3" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC3" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BD3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF3"/>
       <c r="BI3" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BJ3" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BK3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BM3"/>
       <c r="BP3" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BQ3" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BR3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:71" s="1" customFormat="1">
+    <row r="4" spans="1:73" s="1" customFormat="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3460,96 +3482,96 @@
         <v>45902.612789351901</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="17">
         <v>45847</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W4"/>
       <c r="X4" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AA4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB4" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="AD4"/>
       <c r="AE4" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AK4"/>
       <c r="AL4" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AN4" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AR4"/>
       <c r="AU4" s="3"/>
@@ -3568,10 +3590,10 @@
       <c r="BQ4" s="3"/>
       <c r="BR4" s="3"/>
       <c r="BS4" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:71" s="1" customFormat="1">
+    <row r="5" spans="1:73" s="1" customFormat="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3582,80 +3604,80 @@
         <v>45958.426967592597</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="17">
         <v>45708</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W5"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AD5"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK5"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AO5" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP5" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="AP5" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="AR5"/>
       <c r="AU5" s="3"/>
@@ -3674,7 +3696,7 @@
       <c r="BQ5" s="3"/>
       <c r="BR5" s="3"/>
     </row>
-    <row r="6" spans="1:71" s="1" customFormat="1">
+    <row r="6" spans="1:73" s="1" customFormat="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3685,126 +3707,126 @@
         <v>45958.4317592593</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="17">
         <v>45706</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P6" s="16"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W6"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AD6"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI6" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI6" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="AK6"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AO6" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP6" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AR6"/>
       <c r="AU6" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AV6" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AW6" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AY6"/>
       <c r="BB6" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BC6" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BD6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="BF6"/>
       <c r="BI6" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BJ6" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK6" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BM6"/>
       <c r="BP6" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BQ6" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BR6" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS6" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:71">
+    <row r="7" spans="1:73">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3815,144 +3837,146 @@
         <v>45959.692442129599</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="17">
         <v>45796</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L7" s="2">
         <v>45843</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="16"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC7" s="1"/>
       <c r="AD7"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AQ7" s="1"/>
       <c r="AR7"/>
       <c r="AS7" s="1"/>
       <c r="AT7" s="1"/>
       <c r="AU7" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AV7" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AW7" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AX7" s="1"/>
       <c r="AY7"/>
       <c r="AZ7" s="1"/>
       <c r="BA7" s="1"/>
       <c r="BB7" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BC7" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BD7" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BE7" s="1"/>
       <c r="BF7"/>
       <c r="BG7" s="1"/>
       <c r="BH7" s="1"/>
       <c r="BI7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="BJ7" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK7" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BL7" s="1"/>
       <c r="BN7" s="1"/>
       <c r="BO7" s="1"/>
       <c r="BP7" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BQ7" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BR7" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS7" s="10" t="s">
-        <v>148</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
     </row>
-    <row r="8" spans="1:71">
+    <row r="8" spans="1:73">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3963,140 +3987,142 @@
         <v>45959.704907407402</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="17">
         <v>45714</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V8" s="1"/>
       <c r="W8"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC8" s="1"/>
       <c r="AD8"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AH8" s="3" t="s">
+      <c r="AI8" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AQ8" s="1"/>
       <c r="AR8"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AV8" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AW8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AX8" s="1"/>
       <c r="AY8"/>
       <c r="AZ8" s="1"/>
       <c r="BA8" s="1"/>
       <c r="BB8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC8" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BD8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE8" s="1"/>
       <c r="BF8"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
       <c r="BI8" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BJ8" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BK8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BL8" s="1"/>
       <c r="BN8" s="1"/>
       <c r="BO8" s="1"/>
       <c r="BP8" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BQ8" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BR8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS8" s="1"/>
+      <c r="BT8" s="1"/>
+      <c r="BU8" s="1"/>
     </row>
-    <row r="9" spans="1:71">
+    <row r="9" spans="1:73">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4107,61 +4133,61 @@
         <v>45959.715381944399</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F9" s="17">
         <v>45875</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L9" s="2">
         <v>45960</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="16"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V9" s="1"/>
       <c r="W9"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC9" s="1"/>
       <c r="AD9"/>
@@ -4205,10 +4231,12 @@
       <c r="BQ9" s="3"/>
       <c r="BR9" s="3"/>
       <c r="BS9" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="BT9" s="1"/>
+      <c r="BU9" s="1"/>
     </row>
-    <row r="10" spans="1:71">
+    <row r="10" spans="1:73">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4219,142 +4247,144 @@
         <v>45960.369016203702</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F10" s="17">
         <v>45799</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC10" s="1"/>
       <c r="AD10"/>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AH10" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="AI10" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AJ10" s="1"/>
       <c r="AK10"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
       <c r="AN10" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AO10" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AP10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AQ10" s="1"/>
       <c r="AR10"/>
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
       <c r="AU10" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AV10" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AW10" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AX10" s="1"/>
       <c r="AY10"/>
       <c r="AZ10" s="1"/>
       <c r="BA10" s="1"/>
       <c r="BB10" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BC10" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BD10" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BE10" s="1"/>
       <c r="BF10"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
       <c r="BI10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BJ10" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK10" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BL10" s="1"/>
       <c r="BN10" s="1"/>
       <c r="BO10" s="1"/>
       <c r="BP10" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BQ10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="BR10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS10" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="BT10" s="1"/>
+      <c r="BU10" s="1"/>
     </row>
-    <row r="11" spans="1:71">
+    <row r="11" spans="1:73">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4365,142 +4395,144 @@
         <v>45960.372916666704</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="17">
         <v>45797</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ11" s="1"/>
       <c r="AK11"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AP11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AQ11" s="1"/>
       <c r="AR11"/>
       <c r="AS11" s="1"/>
       <c r="AT11" s="1"/>
       <c r="AU11" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AV11" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AW11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX11" s="1"/>
       <c r="AY11"/>
       <c r="AZ11" s="1"/>
       <c r="BA11" s="1"/>
       <c r="BB11" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BC11" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BD11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE11" s="1"/>
       <c r="BF11"/>
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
       <c r="BI11" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BJ11" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK11" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BL11" s="1"/>
       <c r="BN11" s="1"/>
       <c r="BO11" s="1"/>
       <c r="BP11" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BQ11" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BR11" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BS11" s="1" t="s">
-        <v>171</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="BT11" s="1"/>
+      <c r="BU11" s="1"/>
     </row>
-    <row r="12" spans="1:71">
+    <row r="12" spans="1:73">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4511,176 +4543,178 @@
         <v>45960.383090277799</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" s="17">
         <v>45784</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L12" s="2">
         <v>45796</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
       <c r="Q12" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12"/>
       <c r="X12" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC12" s="1"/>
       <c r="AD12"/>
       <c r="AE12" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG12" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AJ12" s="1"/>
       <c r="AK12"/>
       <c r="AL12" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM12" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AN12" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AO12" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AP12" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AQ12" s="1"/>
       <c r="AR12"/>
       <c r="AS12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AT12" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AU12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AV12" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AW12" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AX12" s="1"/>
       <c r="AY12"/>
       <c r="AZ12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="BA12" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="BB12" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BC12" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BD12" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BE12" s="1"/>
       <c r="BF12"/>
       <c r="BG12" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BH12" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BI12" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BJ12" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="BK12" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BL12" s="1"/>
       <c r="BN12" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BO12" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BP12" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BQ12" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="BR12" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BS12" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="BT12" s="1"/>
+      <c r="BU12" s="1"/>
     </row>
-    <row r="13" spans="1:71">
+    <row r="13" spans="1:73">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4691,142 +4725,144 @@
         <v>45960.406053240702</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" s="17">
         <v>45800</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V13" s="1"/>
       <c r="W13"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC13" s="1"/>
       <c r="AD13"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
       <c r="AG13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AJ13" s="1"/>
       <c r="AK13"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AP13" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ13" s="1"/>
       <c r="AR13"/>
       <c r="AS13" s="1"/>
       <c r="AT13" s="1"/>
       <c r="AU13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AV13" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AW13" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AX13" s="1"/>
       <c r="AY13"/>
       <c r="AZ13" s="1"/>
       <c r="BA13" s="1"/>
       <c r="BB13" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BC13" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BD13" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BE13" s="1"/>
       <c r="BF13"/>
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
       <c r="BI13" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BJ13" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK13" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BL13" s="1"/>
       <c r="BN13" s="1"/>
       <c r="BO13" s="1"/>
       <c r="BP13" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BQ13" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="BR13" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS13" s="1" t="s">
-        <v>200</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="BT13" s="1"/>
+      <c r="BU13" s="1"/>
     </row>
-    <row r="14" spans="1:71">
+    <row r="14" spans="1:73">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4837,142 +4873,144 @@
         <v>45960.412141203698</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="17">
         <v>45818</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AJ14" s="1"/>
       <c r="AK14"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AO14" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AP14" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AQ14" s="1"/>
       <c r="AR14"/>
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
       <c r="AU14" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AV14" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AW14" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AX14" s="1"/>
       <c r="AY14"/>
       <c r="AZ14" s="1"/>
       <c r="BA14" s="1"/>
       <c r="BB14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BC14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BE14" s="1"/>
       <c r="BF14"/>
       <c r="BG14" s="1"/>
       <c r="BH14" s="1"/>
       <c r="BI14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BJ14" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BK14" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BL14" s="1"/>
       <c r="BN14" s="1"/>
       <c r="BO14" s="1"/>
       <c r="BP14" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BQ14" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR14" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BS14" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="BT14" s="1"/>
+      <c r="BU14" s="1"/>
     </row>
-    <row r="15" spans="1:71">
+    <row r="15" spans="1:73">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4983,142 +5021,144 @@
         <v>45960.424756944398</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" s="17">
         <v>45869</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC15" s="1"/>
       <c r="AD15"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AJ15" s="1"/>
       <c r="AK15"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AO15" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AP15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ15" s="1"/>
       <c r="AR15"/>
       <c r="AS15" s="1"/>
       <c r="AT15" s="1"/>
       <c r="AU15" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AV15" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AW15" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AX15" s="1"/>
       <c r="AY15"/>
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
       <c r="BB15" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BC15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BD15" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BE15" s="1"/>
       <c r="BF15"/>
       <c r="BG15" s="1"/>
       <c r="BH15" s="1"/>
       <c r="BI15" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BJ15" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BK15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BL15" s="1"/>
       <c r="BN15" s="1"/>
       <c r="BO15" s="1"/>
       <c r="BP15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="BQ15" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BR15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BS15" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="BT15" s="1"/>
+      <c r="BU15" s="1"/>
     </row>
-    <row r="16" spans="1:71">
+    <row r="16" spans="1:73">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -5129,142 +5169,144 @@
         <v>45960.435439814799</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" s="17">
         <v>45861</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="16"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="12"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC16" s="1"/>
       <c r="AD16"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AI16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ16" s="1"/>
       <c r="AK16"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AP16" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AQ16" s="1"/>
       <c r="AR16"/>
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
       <c r="AU16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AV16" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AW16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX16" s="1"/>
       <c r="AY16"/>
       <c r="AZ16" s="1"/>
       <c r="BA16" s="1"/>
       <c r="BB16" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC16" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BD16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE16" s="1"/>
       <c r="BF16"/>
       <c r="BG16" s="1"/>
       <c r="BH16" s="1"/>
       <c r="BI16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BJ16" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BL16" s="1"/>
       <c r="BN16" s="1"/>
       <c r="BO16" s="1"/>
       <c r="BP16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BQ16" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="BR16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BS16" s="1" t="s">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="BT16" s="1"/>
+      <c r="BU16" s="1"/>
     </row>
-    <row r="17" spans="1:71">
+    <row r="17" spans="1:73">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -5275,85 +5317,85 @@
         <v>45960.438368055598</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="17">
         <v>45876</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="16"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="12"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC17" s="1"/>
       <c r="AD17"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AI17" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AJ17" s="1"/>
       <c r="AK17"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
       <c r="AN17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AO17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AP17" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AQ17" s="1"/>
       <c r="AR17"/>
@@ -5383,10 +5425,12 @@
       <c r="BQ17" s="3"/>
       <c r="BR17" s="3"/>
       <c r="BS17" s="1" t="s">
-        <v>227</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="BT17" s="1"/>
+      <c r="BU17" s="1"/>
     </row>
-    <row r="18" spans="1:71">
+    <row r="18" spans="1:73">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -5397,142 +5441,144 @@
         <v>45960.451979166697</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" s="17">
         <v>45860</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O18" s="1"/>
       <c r="P18" s="16"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="12"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AC18" s="1"/>
       <c r="AD18"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AI18" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ18" s="1"/>
       <c r="AK18"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO18" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AP18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AQ18" s="1"/>
       <c r="AR18"/>
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
       <c r="AU18" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AV18" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AW18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX18" s="1"/>
       <c r="AY18"/>
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
       <c r="BB18" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BC18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BD18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BE18" s="1"/>
       <c r="BF18"/>
       <c r="BG18" s="1"/>
       <c r="BH18" s="1"/>
       <c r="BI18" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="BJ18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK18" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BL18" s="1"/>
       <c r="BN18" s="1"/>
       <c r="BO18" s="1"/>
       <c r="BP18" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BQ18" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BR18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BS18" s="10" t="s">
-        <v>234</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="BT18" s="1"/>
+      <c r="BU18" s="1"/>
     </row>
-    <row r="19" spans="1:71">
+    <row r="19" spans="1:73">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -5543,142 +5589,144 @@
         <v>45960.456840277802</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" s="17">
         <v>45937</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L19" s="2">
         <v>45957</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="16"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="12"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AC19" s="1"/>
       <c r="AD19"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AH19" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AI19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AJ19" s="1"/>
       <c r="AK19"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO19" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AP19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AQ19" s="1"/>
       <c r="AR19"/>
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
       <c r="AU19" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AV19" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AW19" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX19" s="1"/>
       <c r="AY19"/>
       <c r="AZ19" s="1"/>
       <c r="BA19" s="1"/>
       <c r="BB19" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="BC19" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BD19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BE19" s="1"/>
       <c r="BF19"/>
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
       <c r="BI19" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BJ19" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BK19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BL19" s="1"/>
       <c r="BN19" s="1"/>
       <c r="BO19" s="1"/>
       <c r="BP19" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="BQ19" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BR19" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BS19" s="1"/>
+      <c r="BT19" s="1"/>
+      <c r="BU19" s="1"/>
     </row>
-    <row r="20" spans="1:71">
+    <row r="20" spans="1:73">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -5689,182 +5737,184 @@
         <v>45972.426412036999</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" s="17">
         <v>45883</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P20" s="16"/>
       <c r="Q20" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="W20" s="12"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AD20"/>
       <c r="AE20" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AH20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AI20" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AK20"/>
       <c r="AL20" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM20" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AN20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AO20" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AP20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AQ20" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR20"/>
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
       <c r="AU20" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AV20" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AW20" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AY20"/>
       <c r="AZ20" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BA20" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BB20" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BC20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BD20" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BE20" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BF20"/>
       <c r="BG20" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BH20" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BI20" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BJ20" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="BK20" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BL20" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BN20" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BO20" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="BP20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BQ20" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BR20" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BS20" s="11" t="s">
-        <v>258</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="BT20" s="1"/>
+      <c r="BU20" s="1"/>
     </row>
-    <row r="21" spans="1:71">
+    <row r="21" spans="1:73">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -5875,195 +5925,197 @@
         <v>45985.627962963001</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21" s="17">
         <v>45985</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L21" s="2">
         <v>46143</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P21" s="17">
         <v>45410</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="W21" s="28">
         <v>45410</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AB21" s="3"/>
       <c r="AC21" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AD21" s="28">
         <v>45410</v>
       </c>
       <c r="AE21" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG21" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AK21" s="29">
         <v>45410</v>
       </c>
       <c r="AL21" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM21" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AO21" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP21" s="3"/>
       <c r="AQ21" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AR21" s="29">
         <v>45410</v>
       </c>
       <c r="AS21" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AT21" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AU21" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AV21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AW21" s="3"/>
       <c r="AX21" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AY21" s="29">
         <v>45410</v>
       </c>
       <c r="AZ21" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BA21" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB21" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="BC21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BD21" s="3"/>
       <c r="BE21" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BF21" s="29">
         <v>45410</v>
       </c>
       <c r="BG21" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="BH21" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="BI21" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="BJ21" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BK21" s="3"/>
       <c r="BL21" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="BM21" s="29">
         <v>45410</v>
       </c>
       <c r="BN21" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="BO21" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BP21" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BQ21" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BR21" s="3"/>
       <c r="BS21" s="11" t="s">
-        <v>285</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="BT21" s="1"/>
+      <c r="BU21" s="1"/>
     </row>
-    <row r="22" spans="1:71">
+    <row r="22" spans="1:73">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -6074,36 +6126,36 @@
         <v>45988.447372685201</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" s="17">
         <v>45987</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P22" s="17">
         <v>45411</v>
@@ -6111,16 +6163,16 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="W22" s="28">
         <v>45410</v>
@@ -6128,16 +6180,16 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AD22" s="29">
         <v>45189</v>
@@ -6145,16 +6197,16 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
       <c r="AG22" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AH22" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AK22" s="29">
         <v>45410</v>
@@ -6162,16 +6214,16 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
       <c r="AN22" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ22" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR22" s="29">
         <v>45410</v>
@@ -6179,16 +6231,16 @@
       <c r="AS22" s="3"/>
       <c r="AT22" s="3"/>
       <c r="AU22" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AV22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AW22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AX22" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AY22" s="29">
         <v>45410</v>
@@ -6196,16 +6248,16 @@
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
       <c r="BB22" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BC22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BD22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BE22" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="BF22" s="29">
         <v>45410</v>
@@ -6213,16 +6265,16 @@
       <c r="BG22" s="3"/>
       <c r="BH22" s="3"/>
       <c r="BI22" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BJ22" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BK22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BL22" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="BM22" s="29">
         <v>45410</v>
@@ -6230,19 +6282,21 @@
       <c r="BN22" s="3"/>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BQ22" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BR22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BS22" s="10" t="s">
-        <v>297</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="BT22" s="1"/>
+      <c r="BU22" s="1"/>
     </row>
-    <row r="23" spans="1:71">
+    <row r="23" spans="1:73">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -6253,99 +6307,99 @@
         <v>45992.711736111101</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F23" s="17">
         <v>45847</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="14"/>
       <c r="L23" s="2"/>
       <c r="M23" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="T23" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="W23" s="12" t="s">
         <v>302</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>300</v>
       </c>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC23" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AH23" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AI23" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AJ23" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AK23" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO23" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AP23" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AQ23" s="1"/>
       <c r="AR23"/>
@@ -6375,10 +6429,12 @@
       <c r="BQ23" s="3"/>
       <c r="BR23" s="3"/>
       <c r="BS23" s="10" t="s">
-        <v>307</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="BT23" s="1"/>
+      <c r="BU23" s="1"/>
     </row>
-    <row r="24" spans="1:71">
+    <row r="24" spans="1:73">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -6389,209 +6445,211 @@
         <v>46035.447673611103</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F24" s="17">
         <v>46035</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L24" s="2">
         <v>46090</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="W24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="AJ24" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="AK24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="AL24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="AM24" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AN24" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP24" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="AQ24" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="AR24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="AS24" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="AT24" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="AU24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AV24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AW24" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="AX24" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="AY24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="AZ24" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BA24" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BB24" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="AD24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="AF24" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI24" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="AJ24" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="AK24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="AL24" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="AM24" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="AN24" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AP24" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="AQ24" s="1" t="s">
+      <c r="BC24" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="BD24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="BE24" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="BF24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="BG24" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="BH24" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BJ24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BK24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="BL24" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="BM24" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="BN24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="BO24" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AR24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="AS24" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="AT24" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="AU24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AW24" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="AX24" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="AY24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="AZ24" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="BA24" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="BB24" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="BC24" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="BD24" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="BE24" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="BF24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="BG24" s="3" t="s">
+      <c r="BP24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BQ24" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="BR24" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="BH24" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="BI24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="BJ24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BK24" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="BL24" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="BM24" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="BN24" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="BO24" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="BP24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BQ24" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="BR24" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="BS24" s="10" t="s">
-        <v>331</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="BT24" s="1"/>
+      <c r="BU24" s="1"/>
     </row>
-    <row r="25" spans="1:71">
+    <row r="25" spans="1:73">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -6602,177 +6660,179 @@
         <v>46042.714189814797</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F25" s="17">
         <v>46042</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L25" s="2">
         <v>46076</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P25" s="18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC25" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AD25" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
       <c r="AG25" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AH25" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AI25" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AJ25" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AK25" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AO25" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AP25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AQ25" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AR25" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AS25" s="3"/>
       <c r="AT25" s="3"/>
       <c r="AU25" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AV25" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AW25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AX25" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AY25" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
       <c r="BB25" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BC25" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BD25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BE25" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="BF25" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
       <c r="BI25" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BJ25" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BL25" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="BM25" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BN25" s="3"/>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BQ25" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BR25" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS25" s="10" t="s">
-        <v>351</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="BT25" s="1"/>
+      <c r="BU25" s="1"/>
     </row>
-    <row r="26" spans="1:71">
+    <row r="26" spans="1:73">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -6783,209 +6843,211 @@
         <v>46092.499652777798</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F26" s="17">
         <v>46092</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="14" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L26" s="2">
         <v>46100</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U26" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="X26" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="V26" s="3" t="s">
+      <c r="Y26" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="AD26" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="AK26" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AL26" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AM26" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="W26" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="AD26" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AE26" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="AF26" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="AG26" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH26" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="AI26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AJ26" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="AK26" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AL26" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="AM26" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="AN26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AO26" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP26" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AR26" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AS26" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AT26" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AU26" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AV26" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AW26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AX26" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="AY26" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AZ26" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BA26" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="AY26" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AZ26" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="BA26" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="BB26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BC26" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="BD26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BE26" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="BF26" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BG26" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BH26" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BI26" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BJ26" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BK26" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="BL26" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="BM26" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BN26" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="BO26" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BP26" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BQ26" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="BR26" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BS26" s="10" t="s">
-        <v>372</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="BT26" s="1"/>
+      <c r="BU26" s="1"/>
     </row>
-    <row r="27" spans="1:71">
+    <row r="27" spans="1:73">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -6996,209 +7058,211 @@
         <v>46105.612777777802</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F27" s="17">
         <v>46099</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L27" s="2">
         <v>46122</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y27" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB27" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="AC27" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AD27" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AK27" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="AF27" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="AG27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ27" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="AK27" s="12" t="s">
-        <v>342</v>
-      </c>
       <c r="AL27" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM27" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AN27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO27" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AQ27" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="AR27" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="AS27" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="AT27" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AU27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AV27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AW27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX27" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="AY27" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="AZ27" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="BA27" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="BB27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="BD27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="BE27" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="BF27" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="BG27" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="BH27" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="BI27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AO27" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="AP27" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="AQ27" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="AR27" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="AS27" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="AT27" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="AU27" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="AV27" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AW27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AX27" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="AY27" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="AZ27" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="BA27" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="BB27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC27" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BD27" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="BE27" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="BF27" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="BG27" s="3" t="s">
+      <c r="BJ27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="BL27" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="BM27" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="BN27" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BH27" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="BI27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BJ27" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BK27" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="BL27" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="BM27" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="BN27" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="BO27" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BP27" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BQ27" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BR27" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="BS27" s="10" t="s">
-        <v>390</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="BT27" s="1"/>
+      <c r="BU27" s="1"/>
     </row>
-    <row r="28" spans="1:71">
+    <row r="28" spans="1:73">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -7209,209 +7273,211 @@
         <v>46108.576412037</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F28" s="17">
         <v>46107</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L28" s="2">
         <v>46126</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P28" s="18" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Z28" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AC28" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AE28" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AF28" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AK28" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="AM28" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="AN28" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="AO28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AP28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ28" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="AR28" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="AS28" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="AT28" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="AU28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV28" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="AW28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AX28" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AY28" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="AG28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI28" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="AJ28" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="AK28" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AL28" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="AM28" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="AN28" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="AO28" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AP28" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AQ28" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="AR28" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AS28" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="AT28" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="AU28" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="AV28" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="AW28" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AX28" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="AY28" s="12" t="s">
-        <v>404</v>
-      </c>
       <c r="AZ28" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="BA28" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="BB28" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC28" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BD28" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE28" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="BF28" s="28">
         <v>45237</v>
       </c>
       <c r="BG28" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BH28" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BI28" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BJ28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK28" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BL28" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="BM28" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BN28" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BO28" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="BP28" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BQ28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BR28" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BS28" s="10" t="s">
-        <v>425</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="BT28" s="1"/>
+      <c r="BU28" s="1"/>
     </row>
-    <row r="29" spans="1:71">
+    <row r="29" spans="1:73">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -7422,177 +7488,179 @@
         <v>46126.573217592602</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F29" s="17">
         <v>46126</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="14" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L29" s="2">
         <v>46134</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P29" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC29" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AH29" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AI29" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ29" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK29" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO29" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP29" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AQ29" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AR29" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AS29" s="3"/>
       <c r="AT29" s="3"/>
       <c r="AU29" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AV29" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AW29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AX29" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AY29" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
       <c r="BB29" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="BC29" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BD29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BE29" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BF29" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
       <c r="BI29" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="BJ29" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BK29" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="BL29" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BM29" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="BQ29" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BR29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BS29" s="10" t="s">
-        <v>441</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="BT29" s="1"/>
+      <c r="BU29" s="1"/>
     </row>
-    <row r="30" spans="1:71">
+    <row r="30" spans="1:73">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -7603,177 +7671,179 @@
         <v>46134.448645833298</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F30" s="17">
         <v>46129</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L30" s="2">
         <v>46148</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AD30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AH30" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AI30" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AJ30" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AK30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
       <c r="AN30" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AO30" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AP30" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AR30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AS30" s="3"/>
       <c r="AT30" s="3"/>
       <c r="AU30" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AV30" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AW30" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AX30" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AY30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
       <c r="BB30" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="BC30" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BD30" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BE30" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BF30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BG30" s="3"/>
       <c r="BH30" s="3"/>
       <c r="BI30" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BJ30" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BK30" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BL30" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BM30" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BN30" s="3"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BQ30" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BR30" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BS30" s="10" t="s">
-        <v>457</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="BT30" s="1"/>
+      <c r="BU30" s="1"/>
     </row>
-    <row r="31" spans="1:71">
+    <row r="31" spans="1:73">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -7784,89 +7854,89 @@
         <v>46139.502731481502</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F31" s="17">
         <v>46135</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L31" s="2">
         <v>46157</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC31" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AD31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
       <c r="AG31" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH31" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AI31" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AJ31" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AK31" s="28">
         <v>45410</v>
@@ -7874,85 +7944,87 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO31" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AP31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ31" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AR31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AS31" s="3"/>
       <c r="AT31" s="3"/>
       <c r="AU31" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AV31" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AW31" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX31" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AY31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
       <c r="BB31" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BC31" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BD31" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BE31" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BF31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BG31" s="3"/>
       <c r="BH31" s="3"/>
       <c r="BI31" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BJ31" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BK31" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BL31" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BM31" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BN31" s="3"/>
       <c r="BO31" s="3"/>
       <c r="BP31" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BQ31" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BR31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BS31" s="10"/>
+      <c r="BT31" s="1"/>
+      <c r="BU31" s="1"/>
     </row>
-    <row r="32" spans="1:71">
+    <row r="32" spans="1:73">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -7963,175 +8035,177 @@
         <v>46148.7254398148</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F32" s="17">
         <v>46146</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="14" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P32" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="W32" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AB32" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC32" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AD32" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AH32" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AI32" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ32" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AK32" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
       <c r="AN32" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO32" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AP32" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ32" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AR32" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AS32" s="3"/>
       <c r="AT32" s="3"/>
       <c r="AU32" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AV32" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AW32" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AX32" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AY32" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="3"/>
       <c r="BB32" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BC32" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BD32" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BE32" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BF32" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BG32" s="3"/>
       <c r="BH32" s="3"/>
       <c r="BI32" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="BJ32" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BK32" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BL32" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="BM32" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="BN32" s="3"/>
       <c r="BO32" s="3"/>
       <c r="BP32" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BQ32" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="BR32" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BS32" s="10"/>
+      <c r="BT32" s="1"/>
+      <c r="BU32" s="1"/>
     </row>
-    <row r="33" spans="1:71">
+    <row r="33" spans="1:73">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -8142,38 +8216,38 @@
         <v>46154.4005555556</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F33" s="17">
         <v>46140</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L33" s="2">
         <v>46240</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P33" s="26">
         <v>45410</v>
@@ -8181,50 +8255,50 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="W33" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AB33" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC33" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AD33" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
       <c r="AG33" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH33" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AI33" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AJ33" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AK33" s="28">
         <v>45410</v>
@@ -8232,85 +8306,87 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO33" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AP33" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AQ33" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AR33" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AV33" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AW33" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AX33" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AY33" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
       <c r="BB33" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BC33" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BD33" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE33" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="BF33" s="12" t="s">
         <v>491</v>
-      </c>
-      <c r="BF33" s="12" t="s">
-        <v>489</v>
       </c>
       <c r="BG33" s="3"/>
       <c r="BH33" s="3"/>
       <c r="BI33" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BJ33" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="BK33" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BL33" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BM33" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BN33" s="3"/>
       <c r="BO33" s="3"/>
       <c r="BP33" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BQ33" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BR33" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BS33" s="10"/>
+      <c r="BT33" s="1"/>
+      <c r="BU33" s="1"/>
     </row>
-    <row r="34" spans="1:71">
+    <row r="34" spans="1:73">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -8321,38 +8397,38 @@
         <v>46167.737233796302</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F34" s="17">
         <v>46164</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="14" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L34" s="2">
         <v>46223</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P34" s="26">
         <v>45227</v>
@@ -8360,126 +8436,128 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="W34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
       <c r="AG34" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AH34" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AI34" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AJ34" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AK34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AO34" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AP34" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ34" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AR34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV34" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AW34" s="3"/>
       <c r="AX34" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AY34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
       <c r="BB34" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BC34" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="BD34" s="3"/>
       <c r="BE34" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="BF34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BG34" s="3"/>
       <c r="BH34" s="3"/>
       <c r="BI34" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BJ34" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BK34" s="3"/>
       <c r="BL34" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="BM34" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BN34" s="3"/>
       <c r="BO34" s="3"/>
       <c r="BP34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BQ34" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BR34" s="3"/>
       <c r="BS34" s="10" t="s">
-        <v>510</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="BT34" s="1"/>
+      <c r="BU34" s="1"/>
     </row>
-    <row r="35" spans="1:71">
+    <row r="35" spans="1:73">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -8490,38 +8568,38 @@
         <v>46176.598796296297</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F35" s="17">
         <v>46175</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="14" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L35" s="2">
         <v>46258</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P35" s="26">
         <v>45410</v>
@@ -8529,50 +8607,50 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="W35" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA35" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AB35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AC35" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AD35" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AH35" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AI35" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AJ35" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AK35" s="28">
         <v>45410</v>
@@ -8580,85 +8658,87 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AO35" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AP35" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AQ35" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AR35" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AV35" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AW35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AX35" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AY35" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="3"/>
       <c r="BB35" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BC35" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BD35" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE35" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="BF35" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BG35" s="3"/>
       <c r="BH35" s="3"/>
       <c r="BI35" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BJ35" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BK35" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BL35" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="BM35" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BN35" s="3"/>
       <c r="BO35" s="3"/>
       <c r="BP35" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BQ35" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BR35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BS35" s="10"/>
+      <c r="BT35" s="1"/>
+      <c r="BU35" s="1"/>
     </row>
-    <row r="36" spans="1:71">
+    <row r="36" spans="1:73">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -8669,119 +8749,119 @@
         <v>46185.425706018497</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F36" s="17">
         <v>46185</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L36" s="2">
         <v>46188</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T36" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="W36" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="U36" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="W36" s="12" t="s">
-        <v>525</v>
-      </c>
       <c r="X36" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="Z36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AB36" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AC36" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AD36" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AE36" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AF36" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG36" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH36" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AI36" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ36" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AK36" s="12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AL36" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM36" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN36" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AO36" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AP36" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AQ36" s="1"/>
       <c r="AR36" s="12"/>
@@ -8812,8 +8892,10 @@
       <c r="BQ36" s="3"/>
       <c r="BR36" s="3"/>
       <c r="BS36" s="10"/>
+      <c r="BT36" s="1"/>
+      <c r="BU36" s="1"/>
     </row>
-    <row r="37" spans="1:71">
+    <row r="37" spans="1:73">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -8824,165 +8906,167 @@
         <v>46188.458831018499</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F37" s="17">
         <v>46147</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="14" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L37" s="27" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
       <c r="S37" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="W37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AA37" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AD37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
       <c r="AG37" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH37" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AI37" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AJ37" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AK37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO37" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AP37" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AQ37" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AR37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AV37" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AW37" s="3"/>
       <c r="AX37" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AY37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="3"/>
       <c r="BB37" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BC37" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BD37" s="3"/>
       <c r="BE37" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="BF37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BG37" s="3"/>
       <c r="BH37" s="3"/>
       <c r="BI37" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BJ37" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BK37" s="3"/>
       <c r="BL37" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="BM37" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BN37" s="3"/>
       <c r="BO37" s="3"/>
       <c r="BP37" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BQ37" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BR37" s="3"/>
       <c r="BS37" s="10" t="s">
-        <v>546</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="BT37" s="1"/>
+      <c r="BU37" s="1"/>
     </row>
-    <row r="38" spans="1:71">
+    <row r="38" spans="1:73">
       <c r="A38" s="1"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
@@ -9054,8 +9138,10 @@
       <c r="BQ38" s="3"/>
       <c r="BR38" s="3"/>
       <c r="BS38" s="10"/>
+      <c r="BT38" s="1"/>
+      <c r="BU38" s="1"/>
     </row>
-    <row r="39" spans="1:71">
+    <row r="39" spans="1:73">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -9066,171 +9152,173 @@
         <v>46226.559270833299</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F39" s="17">
         <v>46218</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="14"/>
       <c r="L39" s="2"/>
       <c r="M39" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="P39" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AA39" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AB39" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC39" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="AD39" s="12" t="s">
         <v>552</v>
-      </c>
-      <c r="AD39" s="12" t="s">
-        <v>550</v>
       </c>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AH39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AI39" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AJ39" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AK39" s="12" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AO39" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AP39" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AQ39" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AR39" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV39" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AW39" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX39" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AY39" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="3"/>
       <c r="BB39" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BC39" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BD39" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE39" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="BF39" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="BG39" s="3"/>
       <c r="BH39" s="3"/>
       <c r="BI39" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BJ39" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BK39" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BL39" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="BM39" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="BN39" s="3"/>
       <c r="BO39" s="3"/>
       <c r="BP39" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="BQ39" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BR39" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BS39" s="10"/>
+      <c r="BT39" s="1"/>
+      <c r="BU39" s="1"/>
     </row>
-    <row r="40" spans="1:71">
+    <row r="40" spans="1:73">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -9241,34 +9329,34 @@
         <v>46231.6304282407</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F40" s="17">
         <v>46199</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="14"/>
       <c r="L40" s="2"/>
       <c r="M40" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="P40" s="19">
         <v>45858</v>
@@ -9276,16 +9364,16 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="W40" s="15">
         <v>45870</v>
@@ -9293,16 +9381,16 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AB40" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AC40" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AD40" s="15">
         <v>45870</v>
@@ -9310,16 +9398,16 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AH40" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AI40" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AJ40" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AK40" s="15">
         <v>45845</v>
@@ -9327,16 +9415,16 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AP40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AR40" s="15">
         <v>45870</v>
@@ -9344,16 +9432,16 @@
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AV40" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AW40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AX40" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AY40" s="15">
         <v>45870</v>
@@ -9361,16 +9449,16 @@
       <c r="AZ40" s="3"/>
       <c r="BA40" s="3"/>
       <c r="BB40" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BC40" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BD40" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BE40" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="BF40" s="15">
         <v>45839</v>
@@ -9378,16 +9466,16 @@
       <c r="BG40" s="3"/>
       <c r="BH40" s="3"/>
       <c r="BI40" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="BJ40" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BK40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BL40" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="BM40" s="30">
         <v>45870</v>
@@ -9395,24 +9483,26 @@
       <c r="BN40" s="3"/>
       <c r="BO40" s="3"/>
       <c r="BP40" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BQ40" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BR40" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BS40" s="10"/>
+      <c r="BT40" s="1"/>
+      <c r="BU40" s="1"/>
     </row>
-    <row r="41" spans="1:71">
+    <row r="41" spans="1:73">
       <c r="A41" s="5"/>
       <c r="C41" s="23"/>
     </row>
-    <row r="45" spans="1:71">
+    <row r="45" spans="1:73">
       <c r="R45" s="7"/>
     </row>
-    <row r="48" spans="1:71">
+    <row r="48" spans="1:73">
       <c r="O48" s="7"/>
     </row>
   </sheetData>
@@ -9432,15 +9522,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
@@ -9456,6 +9537,15 @@
     </Respons_x00e1_vel>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9686,11 +9776,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dados/Controle de Bancos de Bateria Oficial.xlsx
+++ b/dados/Controle de Bancos de Bateria Oficial.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="749" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C02D59D-3251-4AFE-A741-F1880C75073C}"/>
+  <xr:revisionPtr revIDLastSave="751" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCFE75F4-D69A-43D0-9A38-48CF2E5C2295}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="573">
   <si>
     <t>Id</t>
   </si>
@@ -1728,6 +1728,9 @@
   </si>
   <si>
     <t>Leandro</t>
+  </si>
+  <si>
+    <t>ECJ-FORQ-S07</t>
   </si>
   <si>
     <t>052920B</t>
@@ -2069,7 +2072,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -2088,7 +2091,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
@@ -9347,8 +9350,12 @@
         <v>563</v>
       </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="2"/>
+      <c r="K40" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="L40" s="2">
+        <v>46273</v>
+      </c>
       <c r="M40" s="1" t="s">
         <v>79</v>
       </c>
@@ -9356,7 +9363,7 @@
         <v>92</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P40" s="19">
         <v>45858</v>
@@ -9373,7 +9380,7 @@
         <v>168</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="W40" s="15">
         <v>45870</v>
@@ -9390,7 +9397,7 @@
         <v>121</v>
       </c>
       <c r="AC40" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AD40" s="15">
         <v>45870</v>
@@ -9407,7 +9414,7 @@
         <v>197</v>
       </c>
       <c r="AJ40" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AK40" s="15">
         <v>45845</v>
@@ -9424,7 +9431,7 @@
         <v>168</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AR40" s="15">
         <v>45870</v>
@@ -9441,7 +9448,7 @@
         <v>168</v>
       </c>
       <c r="AX40" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AY40" s="15">
         <v>45870</v>
@@ -9458,7 +9465,7 @@
         <v>197</v>
       </c>
       <c r="BE40" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="BF40" s="15">
         <v>45839</v>
@@ -9475,7 +9482,7 @@
         <v>168</v>
       </c>
       <c r="BL40" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="BM40" s="30">
         <v>45870</v>
@@ -9522,6 +9529,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="337ea2d0-885f-4217-baff-63e0aa38c74f">
@@ -9537,15 +9553,6 @@
     </Respons_x00e1_vel>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9776,11 +9783,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1EBE78-309B-4084-BAC4-28E69AD718B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360178F6-3CFF-461B-9986-D90DFFB5599F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
